--- a/public/Nutzerstudie/Assets/Results/analysis_output/00_Studienauswertung.xlsx
+++ b/public/Nutzerstudie/Assets/Results/analysis_output/00_Studienauswertung.xlsx
@@ -463,7 +463,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Zusammenfassung der H1-Ergebnisse je Visualisierung. 'Anzahl' bezeichnet jeweils die Zahl der berücksichtigten Beobachtungen.</t>
+          <t>Deskriptive Zusammenfassung aller H1-Einzelantworten je Visualisierung. Hier werden auch Antworten aus unvollständigen Dreiergruppen berücksichtigt, solange die jeweilige Einzelaufgabe beantwortet wurde. Die inferenzstatistischen Methodenvergleiche basieren dagegen ausschließlich auf den vollständig gepaarten Aufgaben aus 'H1 Gepaarte Antworten'. 'Anzahl' bezeichnet jeweils die Zahl der berücksichtigten Beobachtungen.</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
   <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="75" customWidth="1" min="1" max="1"/>
+    <col width="58" customWidth="1" min="1" max="1"/>
     <col width="27" customWidth="1" min="2" max="2"/>
     <col width="43" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1541,7 +1541,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Nur das freie Textfeld aus dem Abschlussfeedback. Die H2-Begründungen stehen ausschließlich in 'H2 Regionsauswahl'.</t>
+          <t xml:space="preserve">Nur das freie Textfeld aus dem Abschlussfeedback. </t>
         </is>
       </c>
     </row>
@@ -6731,7 +6731,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Auf Teilnehmer × Visualisierung aggregierte Werte der vollständig gepaarten H1-Aufgaben. Diese Tabelle speist die inferenzstatistischen Tests.</t>
+          <t>Auf Teilnehmer × Visualisierung aggregierte Werte ausschließlich aus vollständig gepaarten H1-Aufgaben. Unvollständige Dreiergruppen wurden vorher entfernt. Dadurch kann die hier ausgewiesene Anzahl berücksichtigter Aufgaben kleiner sein als in 'H1 Übersicht'. Diese Tabelle bildet die direkte Grundlage für Normalitätsprüfung, Gesamtvergleich und gegebenenfalls paarweise Vergleiche.</t>
         </is>
       </c>
     </row>

--- a/public/Nutzerstudie/Assets/Results/analysis_output/00_Studienauswertung.xlsx
+++ b/public/Nutzerstudie/Assets/Results/analysis_output/00_Studienauswertung.xlsx
@@ -25,8 +25,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'H1 Übersicht'!$A$2:$L$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'H1 Einzelantworten'!$A$2:$P$40</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'H1 Gepaarte Antworten'!$A$2:$P$40</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'H1 Teilnehmer Methoden'!$A$2:$G$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'H2 Übersicht'!$A$1:$L$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'H2 Regionsauswahl'!$A$2:$K$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'H2 Auswahlhäufigkeit'!$A$1:$D$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Feedback'!$A$2:$C$4</definedName>
@@ -1533,7 +1531,7 @@
   <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="58" customWidth="1" min="1" max="1"/>
+    <col width="75" customWidth="1" min="1" max="1"/>
     <col width="27" customWidth="1" min="2" max="2"/>
     <col width="43" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1541,7 +1539,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nur das freie Textfeld aus dem Abschlussfeedback. </t>
+          <t>Nur das freie Textfeld aus dem Abschlussfeedback. Die H2-Begründungen stehen ausschließlich in 'H2 Regionsauswahl'.</t>
         </is>
       </c>
     </row>
@@ -6716,114 +6714,75 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:H57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="75" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
     <col width="36" customWidth="1" min="3" max="3"/>
     <col width="35" customWidth="1" min="4" max="4"/>
-    <col width="33" customWidth="1" min="5" max="5"/>
-    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Auf Teilnehmer × Visualisierung aggregierte Werte ausschließlich aus vollständig gepaarten H1-Aufgaben. Unvollständige Dreiergruppen wurden vorher entfernt. Dadurch kann die hier ausgewiesene Anzahl berücksichtigter Aufgaben kleiner sein als in 'H1 Übersicht'. Diese Tabelle bildet die direkte Grundlage für Normalitätsprüfung, Gesamtvergleich und gegebenenfalls paarweise Vergleiche.</t>
+          <t>Absolute H1-Werte und direkt anschließend die ergänzenden Within-Participant-Rangfolgen für Genauigkeit und Antwortzeit.</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Teilnehmer-ID</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Visualisierung</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Mittlere absolute Abweichung</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Mediane absolute Abweichung</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Mittlere Antwortzeit (ms)</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Anzahl Aufgaben</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Anteil exakt</t>
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>1. Absolute Werte pro Teilnehmer und Methode</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>4d19396b-7d8d-4d99-8da7-ded7bf2ae5ef</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>IsoGlyph</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="n">
-        <v>0.527507733391323</v>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>1.54667823548e-05</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>20252.5</v>
-      </c>
-      <c r="F3" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="G3" s="1" t="n">
-        <v>0.75</v>
+          <t>Auf Teilnehmer × Visualisierung aggregierte Werte ausschließlich aus vollständig gepaarten H1-Aufgaben. Diese absoluten Werte bilden die Grundlage der inferenzstatistischen H1-Auswertung.</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>4d19396b-7d8d-4d99-8da7-ded7bf2ae5ef</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>ScaledGlyph</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="n">
-        <v>20.77000053904889</v>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>1.078096916799999e-06</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>22607</v>
-      </c>
-      <c r="F4" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="G4" s="1" t="n">
-        <v>0.5</v>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Teilnehmer-ID</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Visualisierung</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Mittlere absolute Abweichung</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Mediane absolute Abweichung</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Mittlere Antwortzeit (ms)</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Anzahl Aufgaben</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Anteil exakt</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -6834,44 +6793,44 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>VSUP</t>
+          <t>IsoGlyph</t>
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>21.92500091089233</v>
+        <v>0.527507733391323</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>1.821786107949999e-06</v>
+        <v>1.54667823548e-05</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>11801</v>
+        <v>20252.5</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>4</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>69febfea-93f2-4aee-8411-6778d021f078</t>
+          <t>4d19396b-7d8d-4d99-8da7-ded7bf2ae5ef</t>
         </is>
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>IsoGlyph</t>
+          <t>ScaledGlyph</t>
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>86.23250688564912</v>
+        <v>20.77000053904889</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>5.710013727219127</v>
+        <v>1.078096916799999e-06</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>18598</v>
+        <v>22607</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>4</v>
@@ -6883,28 +6842,28 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>69febfea-93f2-4aee-8411-6778d021f078</t>
+          <t>4d19396b-7d8d-4d99-8da7-ded7bf2ae5ef</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>ScaledGlyph</t>
+          <t>VSUP</t>
         </is>
       </c>
       <c r="C7" s="1" t="n">
-        <v>75.89750453641354</v>
+        <v>21.92500091089233</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>75.46500712292151</v>
+        <v>1.821786107949999e-06</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>16844</v>
+        <v>11801</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>4</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="8">
@@ -6915,71 +6874,71 @@
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>VSUP</t>
+          <t>IsoGlyph</t>
         </is>
       </c>
       <c r="C8" s="1" t="n">
-        <v>68.28750151786265</v>
+        <v>86.23250688564912</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>4.500002019195</v>
+        <v>5.710013727219127</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>16513</v>
+        <v>18598</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>4</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>ee65e316-170a-44d6-9f78-450e8ec54ccf</t>
+          <t>69febfea-93f2-4aee-8411-6778d021f078</t>
         </is>
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>IsoGlyph</t>
+          <t>ScaledGlyph</t>
         </is>
       </c>
       <c r="C9" s="1" t="n">
-        <v>96.34250072720218</v>
+        <v>75.89750453641354</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>9.280001034425835</v>
+        <v>75.46500712292151</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>20008.5</v>
+        <v>16844</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>4</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>ee65e316-170a-44d6-9f78-450e8ec54ccf</t>
+          <t>69febfea-93f2-4aee-8411-6778d021f078</t>
         </is>
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>ScaledGlyph</t>
+          <t>VSUP</t>
         </is>
       </c>
       <c r="C10" s="1" t="n">
-        <v>32.59250114601672</v>
+        <v>68.28750151786265</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>21.33500167453413</v>
+        <v>4.500002019195</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>18556.5</v>
+        <v>16513</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>4</v>
@@ -6996,17 +6955,17 @@
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>VSUP</t>
+          <t>IsoGlyph</t>
         </is>
       </c>
       <c r="C11" s="1" t="n">
-        <v>97.66000118065926</v>
+        <v>96.34250072720218</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>4.500001858885</v>
+        <v>9.280001034425835</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>23192</v>
+        <v>20008.5</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>4</v>
@@ -7015,8 +6974,921 @@
         <v>0.25</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>ee65e316-170a-44d6-9f78-450e8ec54ccf</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="n">
+        <v>32.59250114601672</v>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>21.33500167453413</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>18556.5</v>
+      </c>
+      <c r="F12" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="G12" s="1" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>ee65e316-170a-44d6-9f78-450e8ec54ccf</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="n">
+        <v>97.66000118065926</v>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>4.500001858885</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>23192</v>
+      </c>
+      <c r="F13" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="G13" s="1" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>2. Rangfolge Genauigkeit pro Teilnehmer</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>Ergänzende Rangbetrachtung innerhalb derselben Person: Rang 1 entspricht der Methode mit der kleinsten mittleren absoluten Abweichung. Bei Gleichständen werden durchschnittliche Ränge vergeben.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Teilnehmer-ID</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Visualisierung</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Ausgangswert</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Kennzahl</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Rang innerhalb Teilnehmer</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Beste Methode / Gleichstand</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>4d19396b-7d8d-4d99-8da7-ded7bf2ae5ef</t>
+        </is>
+      </c>
+      <c r="B19" s="1" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="C19" s="1" t="n">
+        <v>21.92500091089233</v>
+      </c>
+      <c r="D19" s="1" t="inlineStr">
+        <is>
+          <t>Genauigkeit</t>
+        </is>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F19" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>4d19396b-7d8d-4d99-8da7-ded7bf2ae5ef</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="n">
+        <v>20.77000053904889</v>
+      </c>
+      <c r="D20" s="1" t="inlineStr">
+        <is>
+          <t>Genauigkeit</t>
+        </is>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>4d19396b-7d8d-4d99-8da7-ded7bf2ae5ef</t>
+        </is>
+      </c>
+      <c r="B21" s="1" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="C21" s="1" t="n">
+        <v>0.527507733391323</v>
+      </c>
+      <c r="D21" s="1" t="inlineStr">
+        <is>
+          <t>Genauigkeit</t>
+        </is>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>69febfea-93f2-4aee-8411-6778d021f078</t>
+        </is>
+      </c>
+      <c r="B22" s="1" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="C22" s="1" t="n">
+        <v>68.28750151786265</v>
+      </c>
+      <c r="D22" s="1" t="inlineStr">
+        <is>
+          <t>Genauigkeit</t>
+        </is>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>69febfea-93f2-4aee-8411-6778d021f078</t>
+        </is>
+      </c>
+      <c r="B23" s="1" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="C23" s="1" t="n">
+        <v>75.89750453641354</v>
+      </c>
+      <c r="D23" s="1" t="inlineStr">
+        <is>
+          <t>Genauigkeit</t>
+        </is>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>69febfea-93f2-4aee-8411-6778d021f078</t>
+        </is>
+      </c>
+      <c r="B24" s="1" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="C24" s="1" t="n">
+        <v>86.23250688564912</v>
+      </c>
+      <c r="D24" s="1" t="inlineStr">
+        <is>
+          <t>Genauigkeit</t>
+        </is>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F24" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>ee65e316-170a-44d6-9f78-450e8ec54ccf</t>
+        </is>
+      </c>
+      <c r="B25" s="1" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="C25" s="1" t="n">
+        <v>97.66000118065926</v>
+      </c>
+      <c r="D25" s="1" t="inlineStr">
+        <is>
+          <t>Genauigkeit</t>
+        </is>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F25" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>ee65e316-170a-44d6-9f78-450e8ec54ccf</t>
+        </is>
+      </c>
+      <c r="B26" s="1" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="C26" s="1" t="n">
+        <v>32.59250114601672</v>
+      </c>
+      <c r="D26" s="1" t="inlineStr">
+        <is>
+          <t>Genauigkeit</t>
+        </is>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>ee65e316-170a-44d6-9f78-450e8ec54ccf</t>
+        </is>
+      </c>
+      <c r="B27" s="1" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="C27" s="1" t="n">
+        <v>96.34250072720218</v>
+      </c>
+      <c r="D27" s="1" t="inlineStr">
+        <is>
+          <t>Genauigkeit</t>
+        </is>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="F27" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>3. Zusammenfassung Rangfolge Genauigkeit</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>Über alle Teilnehmer zusammengefasste Rangordnung. Ein kleinerer mittlerer Rang bedeutet tendenziell höhere Genauigkeit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Visualisierung</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Anzahl Teilnehmer</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Mittlerer Rang</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Medianer Rang</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Anzahl beste Methode / Gleichstand</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Anteil beste Methode / Gleichstand</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Kennzahl</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Finale Rangordnung</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="B33" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C33" s="1" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="D33" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E33" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="1" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="G33" s="1" t="inlineStr">
+        <is>
+          <t>Genauigkeit</t>
+        </is>
+      </c>
+      <c r="H33" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="B34" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C34" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D34" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E34" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" s="1" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="G34" s="1" t="inlineStr">
+        <is>
+          <t>Genauigkeit</t>
+        </is>
+      </c>
+      <c r="H34" s="1" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="B35" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C35" s="1" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="D35" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="E35" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" s="1" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="G35" s="1" t="inlineStr">
+        <is>
+          <t>Genauigkeit</t>
+        </is>
+      </c>
+      <c r="H35" s="1" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>4. Rangfolge Antwortzeit pro Teilnehmer</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>Ergänzende Within-Participant-Rangfolge der Antwortzeit. Rang 1 entspricht der schnellsten Methode derselben Person und reduziert damit den Einfluss unterschiedlicher Hardware-/Systemgeschwindigkeiten.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Teilnehmer-ID</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Visualisierung</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Ausgangswert</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Kennzahl</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Rang innerhalb Teilnehmer</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Beste Methode / Gleichstand</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>4d19396b-7d8d-4d99-8da7-ded7bf2ae5ef</t>
+        </is>
+      </c>
+      <c r="B41" s="1" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="C41" s="1" t="n">
+        <v>11801</v>
+      </c>
+      <c r="D41" s="1" t="inlineStr">
+        <is>
+          <t>Antwortzeit</t>
+        </is>
+      </c>
+      <c r="E41" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>4d19396b-7d8d-4d99-8da7-ded7bf2ae5ef</t>
+        </is>
+      </c>
+      <c r="B42" s="1" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="C42" s="1" t="n">
+        <v>22607</v>
+      </c>
+      <c r="D42" s="1" t="inlineStr">
+        <is>
+          <t>Antwortzeit</t>
+        </is>
+      </c>
+      <c r="E42" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F42" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>4d19396b-7d8d-4d99-8da7-ded7bf2ae5ef</t>
+        </is>
+      </c>
+      <c r="B43" s="1" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="C43" s="1" t="n">
+        <v>20252.5</v>
+      </c>
+      <c r="D43" s="1" t="inlineStr">
+        <is>
+          <t>Antwortzeit</t>
+        </is>
+      </c>
+      <c r="E43" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="F43" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>69febfea-93f2-4aee-8411-6778d021f078</t>
+        </is>
+      </c>
+      <c r="B44" s="1" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="C44" s="1" t="n">
+        <v>16513</v>
+      </c>
+      <c r="D44" s="1" t="inlineStr">
+        <is>
+          <t>Antwortzeit</t>
+        </is>
+      </c>
+      <c r="E44" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>69febfea-93f2-4aee-8411-6778d021f078</t>
+        </is>
+      </c>
+      <c r="B45" s="1" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="C45" s="1" t="n">
+        <v>16844</v>
+      </c>
+      <c r="D45" s="1" t="inlineStr">
+        <is>
+          <t>Antwortzeit</t>
+        </is>
+      </c>
+      <c r="E45" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="F45" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>69febfea-93f2-4aee-8411-6778d021f078</t>
+        </is>
+      </c>
+      <c r="B46" s="1" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="C46" s="1" t="n">
+        <v>18598</v>
+      </c>
+      <c r="D46" s="1" t="inlineStr">
+        <is>
+          <t>Antwortzeit</t>
+        </is>
+      </c>
+      <c r="E46" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F46" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>ee65e316-170a-44d6-9f78-450e8ec54ccf</t>
+        </is>
+      </c>
+      <c r="B47" s="1" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="C47" s="1" t="n">
+        <v>23192</v>
+      </c>
+      <c r="D47" s="1" t="inlineStr">
+        <is>
+          <t>Antwortzeit</t>
+        </is>
+      </c>
+      <c r="E47" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F47" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>ee65e316-170a-44d6-9f78-450e8ec54ccf</t>
+        </is>
+      </c>
+      <c r="B48" s="1" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="C48" s="1" t="n">
+        <v>18556.5</v>
+      </c>
+      <c r="D48" s="1" t="inlineStr">
+        <is>
+          <t>Antwortzeit</t>
+        </is>
+      </c>
+      <c r="E48" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>ee65e316-170a-44d6-9f78-450e8ec54ccf</t>
+        </is>
+      </c>
+      <c r="B49" s="1" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="C49" s="1" t="n">
+        <v>20008.5</v>
+      </c>
+      <c r="D49" s="1" t="inlineStr">
+        <is>
+          <t>Antwortzeit</t>
+        </is>
+      </c>
+      <c r="E49" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="F49" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>5. Zusammenfassung Rangfolge Antwortzeit</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>Über alle Teilnehmer zusammengefasste Zeit-Rangordnung. Ein kleinerer mittlerer Rang bedeutet tendenziell schnellere Bearbeitung.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Visualisierung</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Anzahl Teilnehmer</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Mittlerer Rang</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Medianer Rang</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Anzahl beste Methode / Gleichstand</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Anteil beste Methode / Gleichstand</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>Kennzahl</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>Finale Rangordnung</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="B55" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C55" s="1" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="D55" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="F55" s="1" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="G55" s="1" t="inlineStr">
+        <is>
+          <t>Antwortzeit</t>
+        </is>
+      </c>
+      <c r="H55" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="B56" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C56" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D56" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E56" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F56" s="1" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="G56" s="1" t="inlineStr">
+        <is>
+          <t>Antwortzeit</t>
+        </is>
+      </c>
+      <c r="H56" s="1" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="B57" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C57" s="1" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="D57" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E57" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="1" t="inlineStr">
+        <is>
+          <t>Antwortzeit</t>
+        </is>
+      </c>
+      <c r="H57" s="1" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:G11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7613,16 +8485,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="75" customWidth="1" min="1" max="1"/>
     <col width="29" customWidth="1" min="2" max="2"/>
     <col width="38" customWidth="1" min="3" max="3"/>
-    <col width="37" customWidth="1" min="4" max="4"/>
-    <col width="31" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="38" customWidth="1" min="7" max="7"/>
+    <col width="41" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="41" customWidth="1" min="7" max="7"/>
     <col width="37" customWidth="1" min="8" max="8"/>
     <col width="33" customWidth="1" min="9" max="9"/>
     <col width="32" customWidth="1" min="10" max="10"/>
@@ -7631,189 +8503,1499 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Visualisierung</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Anzahl Entscheidungen</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>Mittlere gewählte Unsicherheit</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>Mediane gewählte Unsicherheit</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>Mittlere Zielabweichung</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>Mediane Zielabweichung</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>Mittlere subjektive Sicherheit</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>Mediane subjektive Sicherheit</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>Mittlere Antwortzeit (ms)</t>
-        </is>
-      </c>
-      <c r="J1" s="2" t="inlineStr">
-        <is>
-          <t>Mediane Antwortzeit (ms)</t>
-        </is>
-      </c>
-      <c r="K1" s="2" t="inlineStr">
-        <is>
-          <t>Anteil sicherste Region gewählt</t>
-        </is>
-      </c>
-      <c r="L1" s="2" t="inlineStr">
-        <is>
-          <t>Auswertbare Entscheidungen</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Absolute H2-Ergebnisse und direkt anschließend ergänzende Within-Participant-Rangfolgen für Unsicherheit, Zielabweichung und Antwortzeit.</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>IsoGlyph</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="C2" s="1" t="n">
-        <v>1.7319748712</v>
-      </c>
-      <c r="D2" s="1" t="n">
-        <v>1.424277884</v>
-      </c>
-      <c r="E2" s="1" t="n">
-        <v>11.41034957261333</v>
-      </c>
-      <c r="F2" s="1" t="n">
-        <v>11.05134908984</v>
-      </c>
-      <c r="G2" s="1" t="n">
-        <v>5.666666666666667</v>
-      </c>
-      <c r="H2" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="I2" s="1" t="n">
-        <v>48932.66666666666</v>
-      </c>
-      <c r="J2" s="1" t="n">
-        <v>43866</v>
-      </c>
-      <c r="K2" s="1" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="L2" s="1" t="n">
-        <v>3</v>
+          <t>1. Absolute/deskriptive Werte nach Methode</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
+          <t>Zusammenfassung der tatsächlich gewählten Regionen und ihrer Unsicherheit, Zielabweichung, subjektiven Sicherheit und Antwortzeit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Visualisierung</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Anzahl Entscheidungen</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Mittlere gewählte Unsicherheit</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Mediane gewählte Unsicherheit</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Mittlere Zielabweichung</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Mediane Zielabweichung</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Mittlere subjektive Sicherheit</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Mediane subjektive Sicherheit</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Mittlere Antwortzeit (ms)</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Mediane Antwortzeit (ms)</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Anteil sicherste Region gewählt</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Auswertbare Entscheidungen</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>1.7319748712</v>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>1.424277884</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>11.41034957261333</v>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>11.05134908984</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>5.666666666666667</v>
+      </c>
+      <c r="H5" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="I5" s="1" t="n">
+        <v>48932.66666666666</v>
+      </c>
+      <c r="J5" s="1" t="n">
+        <v>43866</v>
+      </c>
+      <c r="K5" s="1" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="L5" s="1" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
           <t>ScaledGlyph</t>
         </is>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B6" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C6" s="1" t="n">
         <v>3.19965337</v>
       </c>
-      <c r="D3" s="1" t="n">
+      <c r="D6" s="1" t="n">
         <v>3.080212368</v>
       </c>
-      <c r="E3" s="1" t="n">
+      <c r="E6" s="1" t="n">
         <v>6.806759380933333</v>
       </c>
-      <c r="F3" s="1" t="n">
+      <c r="F6" s="1" t="n">
         <v>7.99693754</v>
       </c>
-      <c r="G3" s="1" t="n">
+      <c r="G6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="H3" s="1" t="n">
+      <c r="H6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="I3" s="1" t="n">
+      <c r="I6" s="1" t="n">
         <v>48860.33333333334</v>
       </c>
-      <c r="J3" s="1" t="n">
+      <c r="J6" s="1" t="n">
         <v>49140</v>
       </c>
-      <c r="K3" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" s="1" t="n">
+      <c r="K6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="1" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>VSUP</t>
         </is>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B7" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C7" s="1" t="n">
         <v>3.333614046666666</v>
       </c>
-      <c r="D4" s="1" t="n">
+      <c r="D7" s="1" t="n">
         <v>3.135608284</v>
       </c>
-      <c r="E4" s="1" t="n">
+      <c r="E7" s="1" t="n">
         <v>6.682401515306666</v>
       </c>
-      <c r="F4" s="1" t="n">
+      <c r="F7" s="1" t="n">
         <v>8.096171719999999</v>
       </c>
-      <c r="G4" s="1" t="n">
+      <c r="G7" s="1" t="n">
         <v>5.333333333333333</v>
       </c>
-      <c r="H4" s="1" t="n">
+      <c r="H7" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="I4" s="1" t="n">
+      <c r="I7" s="1" t="n">
         <v>52000.66666666666</v>
       </c>
-      <c r="J4" s="1" t="n">
+      <c r="J7" s="1" t="n">
         <v>55819</v>
       </c>
-      <c r="K4" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="1" t="n">
+      <c r="K7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="1" t="n">
         <v>3</v>
       </c>
     </row>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>2. Rangfolge Unsicherheit pro Teilnehmer</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Rang 1 entspricht innerhalb derselben Person der Methode, unter der die Region mit der geringsten Unsicherheit gewählt wurde.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Teilnehmer-ID</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Visualisierung</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Ausgangswert</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Kennzahl</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Rang innerhalb Teilnehmer</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Beste Methode / Gleichstand</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>4d19396b-7d8d-4d99-8da7-ded7bf2ae5ef</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="n">
+        <v>3.135608284</v>
+      </c>
+      <c r="D13" s="1" t="inlineStr">
+        <is>
+          <t>Unsicherheit der gewählten Region</t>
+        </is>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>4d19396b-7d8d-4d99-8da7-ded7bf2ae5ef</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="n">
+        <v>3.080212368</v>
+      </c>
+      <c r="D14" s="1" t="inlineStr">
+        <is>
+          <t>Unsicherheit der gewählten Region</t>
+        </is>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>4d19396b-7d8d-4d99-8da7-ded7bf2ae5ef</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>1.424277884</v>
+      </c>
+      <c r="D15" s="1" t="inlineStr">
+        <is>
+          <t>Unsicherheit der gewählten Region</t>
+        </is>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>69febfea-93f2-4aee-8411-6778d021f078</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="C16" s="1" t="n">
+        <v>5.4355829</v>
+      </c>
+      <c r="D16" s="1" t="inlineStr">
+        <is>
+          <t>Unsicherheit der gewählten Region</t>
+        </is>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>69febfea-93f2-4aee-8411-6778d021f078</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="n">
+        <v>5.06290306</v>
+      </c>
+      <c r="D17" s="1" t="inlineStr">
+        <is>
+          <t>Unsicherheit der gewählten Region</t>
+        </is>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>69febfea-93f2-4aee-8411-6778d021f078</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="n">
+        <v>3.129501516</v>
+      </c>
+      <c r="D18" s="1" t="inlineStr">
+        <is>
+          <t>Unsicherheit der gewählten Region</t>
+        </is>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>ee65e316-170a-44d6-9f78-450e8ec54ccf</t>
+        </is>
+      </c>
+      <c r="B19" s="1" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="C19" s="1" t="n">
+        <v>1.429650956</v>
+      </c>
+      <c r="D19" s="1" t="inlineStr">
+        <is>
+          <t>Unsicherheit der gewählten Region</t>
+        </is>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>ee65e316-170a-44d6-9f78-450e8ec54ccf</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="n">
+        <v>1.455844682</v>
+      </c>
+      <c r="D20" s="1" t="inlineStr">
+        <is>
+          <t>Unsicherheit der gewählten Region</t>
+        </is>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F20" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>ee65e316-170a-44d6-9f78-450e8ec54ccf</t>
+        </is>
+      </c>
+      <c r="B21" s="1" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="C21" s="1" t="n">
+        <v>0.6421452136</v>
+      </c>
+      <c r="D21" s="1" t="inlineStr">
+        <is>
+          <t>Unsicherheit der gewählten Region</t>
+        </is>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>3. Zusammenfassung Rangfolge Unsicherheit</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Über alle Teilnehmer zusammengefasste Rangordnung der gewählten Unsicherheit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Visualisierung</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Anzahl Teilnehmer</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Mittlerer Rang</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Medianer Rang</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Anzahl beste Methode / Gleichstand</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Anteil beste Methode / Gleichstand</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Kennzahl</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Finale Rangordnung</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="B27" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C27" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F27" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" s="1" t="inlineStr">
+        <is>
+          <t>Unsicherheit der gewählten Region</t>
+        </is>
+      </c>
+      <c r="H27" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="B28" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C28" s="1" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="1" t="inlineStr">
+        <is>
+          <t>Unsicherheit der gewählten Region</t>
+        </is>
+      </c>
+      <c r="H28" s="1" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="B29" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C29" s="1" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="D29" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="E29" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="1" t="inlineStr">
+        <is>
+          <t>Unsicherheit der gewählten Region</t>
+        </is>
+      </c>
+      <c r="H29" s="1" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>4. Rangfolge Zielabweichung pro Teilnehmer</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>Rang 1 entspricht der Methode mit der kleinsten Abweichung der gewählten Region vom Zielwert -12 °C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Teilnehmer-ID</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Visualisierung</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Ausgangswert</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Kennzahl</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Rang innerhalb Teilnehmer</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Beste Methode / Gleichstand</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>4d19396b-7d8d-4d99-8da7-ded7bf2ae5ef</t>
+        </is>
+      </c>
+      <c r="B35" s="1" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="C35" s="1" t="n">
+        <v>10.76092652592</v>
+      </c>
+      <c r="D35" s="1" t="inlineStr">
+        <is>
+          <t>Abweichung vom Zielwert -12 °C</t>
+        </is>
+      </c>
+      <c r="E35" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="F35" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>4d19396b-7d8d-4d99-8da7-ded7bf2ae5ef</t>
+        </is>
+      </c>
+      <c r="B36" s="1" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="C36" s="1" t="n">
+        <v>11.0990278568</v>
+      </c>
+      <c r="D36" s="1" t="inlineStr">
+        <is>
+          <t>Abweichung vom Zielwert -12 °C</t>
+        </is>
+      </c>
+      <c r="E36" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F36" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>4d19396b-7d8d-4d99-8da7-ded7bf2ae5ef</t>
+        </is>
+      </c>
+      <c r="B37" s="1" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="C37" s="1" t="n">
+        <v>8.395103607999999</v>
+      </c>
+      <c r="D37" s="1" t="inlineStr">
+        <is>
+          <t>Abweichung vom Zielwert -12 °C</t>
+        </is>
+      </c>
+      <c r="E37" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>69febfea-93f2-4aee-8411-6778d021f078</t>
+        </is>
+      </c>
+      <c r="B38" s="1" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="C38" s="1" t="n">
+        <v>1.1901063</v>
+      </c>
+      <c r="D38" s="1" t="inlineStr">
+        <is>
+          <t>Abweichung vom Zielwert -12 °C</t>
+        </is>
+      </c>
+      <c r="E38" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>69febfea-93f2-4aee-8411-6778d021f078</t>
+        </is>
+      </c>
+      <c r="B39" s="1" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="C39" s="1" t="n">
+        <v>1.324312746</v>
+      </c>
+      <c r="D39" s="1" t="inlineStr">
+        <is>
+          <t>Abweichung vom Zielwert -12 °C</t>
+        </is>
+      </c>
+      <c r="E39" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="F39" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>69febfea-93f2-4aee-8411-6778d021f078</t>
+        </is>
+      </c>
+      <c r="B40" s="1" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="C40" s="1" t="n">
+        <v>11.05134908984</v>
+      </c>
+      <c r="D40" s="1" t="inlineStr">
+        <is>
+          <t>Abweichung vom Zielwert -12 °C</t>
+        </is>
+      </c>
+      <c r="E40" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F40" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>ee65e316-170a-44d6-9f78-450e8ec54ccf</t>
+        </is>
+      </c>
+      <c r="B41" s="1" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="C41" s="1" t="n">
+        <v>8.096171719999999</v>
+      </c>
+      <c r="D41" s="1" t="inlineStr">
+        <is>
+          <t>Abweichung vom Zielwert -12 °C</t>
+        </is>
+      </c>
+      <c r="E41" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="F41" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>ee65e316-170a-44d6-9f78-450e8ec54ccf</t>
+        </is>
+      </c>
+      <c r="B42" s="1" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="C42" s="1" t="n">
+        <v>7.99693754</v>
+      </c>
+      <c r="D42" s="1" t="inlineStr">
+        <is>
+          <t>Abweichung vom Zielwert -12 °C</t>
+        </is>
+      </c>
+      <c r="E42" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>ee65e316-170a-44d6-9f78-450e8ec54ccf</t>
+        </is>
+      </c>
+      <c r="B43" s="1" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="C43" s="1" t="n">
+        <v>14.78459602</v>
+      </c>
+      <c r="D43" s="1" t="inlineStr">
+        <is>
+          <t>Abweichung vom Zielwert -12 °C</t>
+        </is>
+      </c>
+      <c r="E43" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F43" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>5. Zusammenfassung Rangfolge Zielabweichung</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>Über alle Teilnehmer zusammengefasste Rangordnung der Zielabweichung.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Visualisierung</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Anzahl Teilnehmer</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Mittlerer Rang</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Medianer Rang</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Anzahl beste Methode / Gleichstand</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Anteil beste Methode / Gleichstand</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Kennzahl</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>Finale Rangordnung</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="B49" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C49" s="1" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="D49" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E49" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" s="1" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="G49" s="1" t="inlineStr">
+        <is>
+          <t>Abweichung vom Zielwert -12 °C</t>
+        </is>
+      </c>
+      <c r="H49" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="B50" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C50" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D50" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E50" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" s="1" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="G50" s="1" t="inlineStr">
+        <is>
+          <t>Abweichung vom Zielwert -12 °C</t>
+        </is>
+      </c>
+      <c r="H50" s="1" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="B51" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C51" s="1" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="D51" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="E51" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" s="1" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="G51" s="1" t="inlineStr">
+        <is>
+          <t>Abweichung vom Zielwert -12 °C</t>
+        </is>
+      </c>
+      <c r="H51" s="1" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>6. Rangfolge Antwortzeit pro Teilnehmer</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>Rang 1 entspricht der schnellsten Regionsentscheidung innerhalb derselben Person; dadurch werden Unterschiede zwischen den Hardware-/Systemgeschwindigkeiten weniger relevant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Teilnehmer-ID</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Visualisierung</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Ausgangswert</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Kennzahl</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Rang innerhalb Teilnehmer</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Beste Methode / Gleichstand</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>4d19396b-7d8d-4d99-8da7-ded7bf2ae5ef</t>
+        </is>
+      </c>
+      <c r="B57" s="1" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="C57" s="1" t="n">
+        <v>55819</v>
+      </c>
+      <c r="D57" s="1" t="inlineStr">
+        <is>
+          <t>Antwortzeit</t>
+        </is>
+      </c>
+      <c r="E57" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="F57" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>4d19396b-7d8d-4d99-8da7-ded7bf2ae5ef</t>
+        </is>
+      </c>
+      <c r="B58" s="1" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="C58" s="1" t="n">
+        <v>45428</v>
+      </c>
+      <c r="D58" s="1" t="inlineStr">
+        <is>
+          <t>Antwortzeit</t>
+        </is>
+      </c>
+      <c r="E58" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F58" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
+        <is>
+          <t>4d19396b-7d8d-4d99-8da7-ded7bf2ae5ef</t>
+        </is>
+      </c>
+      <c r="B59" s="1" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="C59" s="1" t="n">
+        <v>66632</v>
+      </c>
+      <c r="D59" s="1" t="inlineStr">
+        <is>
+          <t>Antwortzeit</t>
+        </is>
+      </c>
+      <c r="E59" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F59" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="inlineStr">
+        <is>
+          <t>69febfea-93f2-4aee-8411-6778d021f078</t>
+        </is>
+      </c>
+      <c r="B60" s="1" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="C60" s="1" t="n">
+        <v>28302</v>
+      </c>
+      <c r="D60" s="1" t="inlineStr">
+        <is>
+          <t>Antwortzeit</t>
+        </is>
+      </c>
+      <c r="E60" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F60" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="inlineStr">
+        <is>
+          <t>69febfea-93f2-4aee-8411-6778d021f078</t>
+        </is>
+      </c>
+      <c r="B61" s="1" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="C61" s="1" t="n">
+        <v>49140</v>
+      </c>
+      <c r="D61" s="1" t="inlineStr">
+        <is>
+          <t>Antwortzeit</t>
+        </is>
+      </c>
+      <c r="E61" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F61" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="inlineStr">
+        <is>
+          <t>69febfea-93f2-4aee-8411-6778d021f078</t>
+        </is>
+      </c>
+      <c r="B62" s="1" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="C62" s="1" t="n">
+        <v>36300</v>
+      </c>
+      <c r="D62" s="1" t="inlineStr">
+        <is>
+          <t>Antwortzeit</t>
+        </is>
+      </c>
+      <c r="E62" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="F62" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="inlineStr">
+        <is>
+          <t>ee65e316-170a-44d6-9f78-450e8ec54ccf</t>
+        </is>
+      </c>
+      <c r="B63" s="1" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="C63" s="1" t="n">
+        <v>71881</v>
+      </c>
+      <c r="D63" s="1" t="inlineStr">
+        <is>
+          <t>Antwortzeit</t>
+        </is>
+      </c>
+      <c r="E63" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F63" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="inlineStr">
+        <is>
+          <t>ee65e316-170a-44d6-9f78-450e8ec54ccf</t>
+        </is>
+      </c>
+      <c r="B64" s="1" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="C64" s="1" t="n">
+        <v>52013</v>
+      </c>
+      <c r="D64" s="1" t="inlineStr">
+        <is>
+          <t>Antwortzeit</t>
+        </is>
+      </c>
+      <c r="E64" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="F64" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="inlineStr">
+        <is>
+          <t>ee65e316-170a-44d6-9f78-450e8ec54ccf</t>
+        </is>
+      </c>
+      <c r="B65" s="1" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="C65" s="1" t="n">
+        <v>43866</v>
+      </c>
+      <c r="D65" s="1" t="inlineStr">
+        <is>
+          <t>Antwortzeit</t>
+        </is>
+      </c>
+      <c r="E65" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F65" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68">
+      <c r="A68" s="1" t="inlineStr">
+        <is>
+          <t>7. Zusammenfassung Rangfolge Antwortzeit</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="inlineStr">
+        <is>
+          <t>Über alle Teilnehmer zusammengefasste Zeit-Rangordnung der H2-Aufgabe.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Visualisierung</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Anzahl Teilnehmer</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Mittlerer Rang</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Medianer Rang</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Anzahl beste Methode / Gleichstand</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>Anteil beste Methode / Gleichstand</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>Kennzahl</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>Finale Rangordnung</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="B71" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C71" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D71" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E71" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F71" s="1" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="G71" s="1" t="inlineStr">
+        <is>
+          <t>Antwortzeit</t>
+        </is>
+      </c>
+      <c r="H71" s="1" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="B72" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C72" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D72" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E72" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F72" s="1" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="G72" s="1" t="inlineStr">
+        <is>
+          <t>Antwortzeit</t>
+        </is>
+      </c>
+      <c r="H72" s="1" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="B73" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C73" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D73" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E73" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F73" s="1" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="G73" s="1" t="inlineStr">
+        <is>
+          <t>Antwortzeit</t>
+        </is>
+      </c>
+      <c r="H73" s="1" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/public/Nutzerstudie/Assets/Results/analysis_output/00_Studienauswertung.xlsx
+++ b/public/Nutzerstudie/Assets/Results/analysis_output/00_Studienauswertung.xlsx
@@ -17,17 +17,19 @@
     <sheet name="H2 Übersicht" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="H2 Regionsauswahl" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="H2 Auswahlhäufigkeit" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="H2 Unsicherheit Statistik" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="H2 Zielabweichung Statistik" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Feedback" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="H2 Teilnehmer Methoden" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="H2 Unsicherheit Statistik" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="H2 Zielabweichung Statistik" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Feedback" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'H1 Übersicht'!$A$2:$L$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'H1 Einzelantworten'!$A$2:$P$40</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'H1 Gepaarte Antworten'!$A$2:$P$40</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'H2 Regionsauswahl'!$A$2:$K$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'H1 Übersicht'!$A$2:$N$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'H1 Einzelantworten'!$A$2:$Q$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'H1 Gepaarte Antworten'!$A$2:$Q$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'H2 Übersicht'!$A$2:$L$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'H2 Regionsauswahl'!$A$2:$K$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'H2 Auswahlhäufigkeit'!$A$1:$D$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Feedback'!$A$2:$C$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Feedback'!$A$2:$C$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -441,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="75" customWidth="1" min="1" max="1"/>
@@ -449,19 +451,21 @@
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="36" customWidth="1" min="4" max="4"/>
     <col width="35" customWidth="1" min="5" max="5"/>
-    <col width="33" customWidth="1" min="6" max="6"/>
-    <col width="32" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="39" customWidth="1" min="10" max="10"/>
-    <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="49" customWidth="1" min="7" max="7"/>
+    <col width="33" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="39" customWidth="1" min="12" max="12"/>
+    <col width="26" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Deskriptive Zusammenfassung aller H1-Einzelantworten je Visualisierung. Hier werden auch Antworten aus unvollständigen Dreiergruppen berücksichtigt, solange die jeweilige Einzelaufgabe beantwortet wurde. Die inferenzstatistischen Methodenvergleiche basieren dagegen ausschließlich auf den vollständig gepaarten Aufgaben aus 'H1 Gepaarte Antworten'. 'Anzahl' bezeichnet jeweils die Zahl der berücksichtigten Beobachtungen.</t>
+          <t>Deskriptive Zusammenfassung aller H1-Einzelantworten je Visualisierung. Zusätzlich zur absoluten Abweichung wird die normalisierte absolute Abweichung (Abweichung geteilt durch die Wertspanne der jeweiligen Variable) ausgewiesen, damit Luftdruck und Niederschlag trotz unterschiedlicher Skalen vergleichbar sind. Hier werden auch Antworten aus unvollständigen Dreiergruppen berücksichtigt, solange die jeweilige Einzelaufgabe beantwortet wurde. Die inferenzstatistischen Methodenvergleiche basieren dagegen ausschließlich auf den vollständig gepaarten Aufgaben aus 'H1 Gepaarte Antworten'. 'Anzahl' bezeichnet jeweils die Zahl der berücksichtigten Beobachtungen.</t>
         </is>
       </c>
     </row>
@@ -493,35 +497,45 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
+          <t>Mittlere normalisierte absolute Abweichung</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Mediane normalisierte absolute Abweichung</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
           <t>Mittlere Antwortzeit (ms)</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>Mediane Antwortzeit (ms)</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>Beantwortungsquote</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>Anzahl exakt</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>Auswertbare Antworten für Exakt</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>Anteil exakt</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>Exakt (Anzahl)</t>
         </is>
@@ -546,24 +560,30 @@
         <v>2.9156035e-05</v>
       </c>
       <c r="F3" s="1" t="n">
+        <v>0.08239977473556627</v>
+      </c>
+      <c r="G3" s="1" t="n">
+        <v>0.007600373555636614</v>
+      </c>
+      <c r="H3" s="1" t="n">
         <v>19619.66666666667</v>
       </c>
-      <c r="G3" s="1" t="n">
+      <c r="I3" s="1" t="n">
         <v>18659.5</v>
       </c>
-      <c r="H3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" s="1" t="n">
+      <c r="J3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="J3" s="1" t="n">
+      <c r="L3" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="K3" s="1" t="n">
+      <c r="M3" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="L3" s="1" t="inlineStr">
+      <c r="N3" s="1" t="inlineStr">
         <is>
           <t>6/12</t>
         </is>
@@ -588,24 +608,30 @@
         <v>9.072836104800001e-06</v>
       </c>
       <c r="F4" s="1" t="n">
+        <v>0.03699449500459839</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>0.02282753680578894</v>
+      </c>
+      <c r="H4" s="1" t="n">
         <v>19335.83333333333</v>
       </c>
-      <c r="G4" s="1" t="n">
+      <c r="I4" s="1" t="n">
         <v>13000.5</v>
       </c>
-      <c r="H4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" s="1" t="n">
+      <c r="J4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="J4" s="1" t="n">
+      <c r="L4" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="K4" s="1" t="n">
+      <c r="M4" s="1" t="n">
         <v>0.25</v>
       </c>
-      <c r="L4" s="1" t="inlineStr">
+      <c r="N4" s="1" t="inlineStr">
         <is>
           <t>3/12</t>
         </is>
@@ -630,31 +656,37 @@
         <v>3.878080000000005e-06</v>
       </c>
       <c r="F5" s="1" t="n">
+        <v>0.0288246818267547</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>0.02258107452897549</v>
+      </c>
+      <c r="H5" s="1" t="n">
         <v>17168.66666666667</v>
       </c>
-      <c r="G5" s="1" t="n">
+      <c r="I5" s="1" t="n">
         <v>14420</v>
       </c>
-      <c r="H5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" s="1" t="n">
+      <c r="J5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="L5" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="K5" s="1" t="n">
+      <c r="M5" s="1" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="L5" s="1" t="inlineStr">
+      <c r="N5" s="1" t="inlineStr">
         <is>
           <t>4/12</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:L5"/>
+  <autoFilter ref="A2:N5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -870,6 +902,1639 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H79"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="75" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="41" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="41" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Analog zu 'H1 Teilnehmer Methoden': zuerst die absoluten Werte je Teilnehmer und Methode, danach die ergänzenden Within-Participant-Rangfolgen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>1. Absolute Werte pro Teilnehmer und Methode</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Direkte H2-Werte je Teilnehmer und Visualisierung. Diese Werte bilden die Grundlage der H2-Methodenvergleiche.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Teilnehmer-ID</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Visualisierung</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Gewählte Region</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Unsicherheit der gewählten Region</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Abweichung vom Zielwert -12 °C</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Subjektive Sicherheit</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Antwortzeit (ms)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>4d19396b-7d8d-4d99-8da7-ded7bf2ae5ef</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>3.135608284</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>10.76092652592</v>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>55819</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>4d19396b-7d8d-4d99-8da7-ded7bf2ae5ef</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>3.080212368</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>11.0990278568</v>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>45428</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>4d19396b-7d8d-4d99-8da7-ded7bf2ae5ef</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>1.424277884</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>8.395103607999999</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>66632</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>69febfea-93f2-4aee-8411-6778d021f078</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>5.4355829</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>1.1901063</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>28302</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>69febfea-93f2-4aee-8411-6778d021f078</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>5.06290306</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>1.324312746</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>49140</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>69febfea-93f2-4aee-8411-6778d021f078</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>3.129501516</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>11.05134908984</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>36300</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>ee65e316-170a-44d6-9f78-450e8ec54ccf</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>1.429650956</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>8.096171719999999</v>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="G11" s="1" t="n">
+        <v>71881</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>ee65e316-170a-44d6-9f78-450e8ec54ccf</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>1.455844682</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>7.99693754</v>
+      </c>
+      <c r="F12" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="G12" s="1" t="n">
+        <v>52013</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>ee65e316-170a-44d6-9f78-450e8ec54ccf</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>0.6421452136</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>14.78459602</v>
+      </c>
+      <c r="F13" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="G13" s="1" t="n">
+        <v>43866</v>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>2. Rangfolge Unsicherheit pro Teilnehmer</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>Rang 1 entspricht innerhalb derselben Person der Methode, unter der die Region mit der geringsten Unsicherheit gewählt wurde.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Teilnehmer-ID</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Visualisierung</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Ausgangswert</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Kennzahl</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Rang innerhalb Teilnehmer</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Beste Methode / Gleichstand</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>4d19396b-7d8d-4d99-8da7-ded7bf2ae5ef</t>
+        </is>
+      </c>
+      <c r="B19" s="1" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="C19" s="1" t="n">
+        <v>3.135608284</v>
+      </c>
+      <c r="D19" s="1" t="inlineStr">
+        <is>
+          <t>Unsicherheit der gewählten Region</t>
+        </is>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F19" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>4d19396b-7d8d-4d99-8da7-ded7bf2ae5ef</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="n">
+        <v>3.080212368</v>
+      </c>
+      <c r="D20" s="1" t="inlineStr">
+        <is>
+          <t>Unsicherheit der gewählten Region</t>
+        </is>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>4d19396b-7d8d-4d99-8da7-ded7bf2ae5ef</t>
+        </is>
+      </c>
+      <c r="B21" s="1" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="C21" s="1" t="n">
+        <v>1.424277884</v>
+      </c>
+      <c r="D21" s="1" t="inlineStr">
+        <is>
+          <t>Unsicherheit der gewählten Region</t>
+        </is>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>69febfea-93f2-4aee-8411-6778d021f078</t>
+        </is>
+      </c>
+      <c r="B22" s="1" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="C22" s="1" t="n">
+        <v>5.4355829</v>
+      </c>
+      <c r="D22" s="1" t="inlineStr">
+        <is>
+          <t>Unsicherheit der gewählten Region</t>
+        </is>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F22" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>69febfea-93f2-4aee-8411-6778d021f078</t>
+        </is>
+      </c>
+      <c r="B23" s="1" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="C23" s="1" t="n">
+        <v>5.06290306</v>
+      </c>
+      <c r="D23" s="1" t="inlineStr">
+        <is>
+          <t>Unsicherheit der gewählten Region</t>
+        </is>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>69febfea-93f2-4aee-8411-6778d021f078</t>
+        </is>
+      </c>
+      <c r="B24" s="1" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="C24" s="1" t="n">
+        <v>3.129501516</v>
+      </c>
+      <c r="D24" s="1" t="inlineStr">
+        <is>
+          <t>Unsicherheit der gewählten Region</t>
+        </is>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>ee65e316-170a-44d6-9f78-450e8ec54ccf</t>
+        </is>
+      </c>
+      <c r="B25" s="1" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="C25" s="1" t="n">
+        <v>1.429650956</v>
+      </c>
+      <c r="D25" s="1" t="inlineStr">
+        <is>
+          <t>Unsicherheit der gewählten Region</t>
+        </is>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="F25" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>ee65e316-170a-44d6-9f78-450e8ec54ccf</t>
+        </is>
+      </c>
+      <c r="B26" s="1" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="C26" s="1" t="n">
+        <v>1.455844682</v>
+      </c>
+      <c r="D26" s="1" t="inlineStr">
+        <is>
+          <t>Unsicherheit der gewählten Region</t>
+        </is>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F26" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>ee65e316-170a-44d6-9f78-450e8ec54ccf</t>
+        </is>
+      </c>
+      <c r="B27" s="1" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="C27" s="1" t="n">
+        <v>0.6421452136</v>
+      </c>
+      <c r="D27" s="1" t="inlineStr">
+        <is>
+          <t>Unsicherheit der gewählten Region</t>
+        </is>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>3. Zusammenfassung Rangfolge Unsicherheit</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>Über alle Teilnehmer zusammengefasste Rangordnung der gewählten Unsicherheit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Visualisierung</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Anzahl Teilnehmer</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Mittlerer Rang</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Medianer Rang</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Anzahl beste Methode / Gleichstand</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Anteil beste Methode / Gleichstand</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Kennzahl</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Finale Rangordnung</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="B33" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C33" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F33" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="1" t="inlineStr">
+        <is>
+          <t>Unsicherheit der gewählten Region</t>
+        </is>
+      </c>
+      <c r="H33" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="B34" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C34" s="1" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="D34" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E34" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="1" t="inlineStr">
+        <is>
+          <t>Unsicherheit der gewählten Region</t>
+        </is>
+      </c>
+      <c r="H34" s="1" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="B35" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C35" s="1" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="D35" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="E35" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="1" t="inlineStr">
+        <is>
+          <t>Unsicherheit der gewählten Region</t>
+        </is>
+      </c>
+      <c r="H35" s="1" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>4. Rangfolge Zielabweichung pro Teilnehmer</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>Rang 1 entspricht der Methode mit der kleinsten Abweichung der gewählten Region vom Zielwert -12 °C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Teilnehmer-ID</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Visualisierung</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Ausgangswert</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Kennzahl</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Rang innerhalb Teilnehmer</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Beste Methode / Gleichstand</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>4d19396b-7d8d-4d99-8da7-ded7bf2ae5ef</t>
+        </is>
+      </c>
+      <c r="B41" s="1" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="C41" s="1" t="n">
+        <v>10.76092652592</v>
+      </c>
+      <c r="D41" s="1" t="inlineStr">
+        <is>
+          <t>Abweichung vom Zielwert -12 °C</t>
+        </is>
+      </c>
+      <c r="E41" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="F41" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>4d19396b-7d8d-4d99-8da7-ded7bf2ae5ef</t>
+        </is>
+      </c>
+      <c r="B42" s="1" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="C42" s="1" t="n">
+        <v>11.0990278568</v>
+      </c>
+      <c r="D42" s="1" t="inlineStr">
+        <is>
+          <t>Abweichung vom Zielwert -12 °C</t>
+        </is>
+      </c>
+      <c r="E42" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F42" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>4d19396b-7d8d-4d99-8da7-ded7bf2ae5ef</t>
+        </is>
+      </c>
+      <c r="B43" s="1" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="C43" s="1" t="n">
+        <v>8.395103607999999</v>
+      </c>
+      <c r="D43" s="1" t="inlineStr">
+        <is>
+          <t>Abweichung vom Zielwert -12 °C</t>
+        </is>
+      </c>
+      <c r="E43" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>69febfea-93f2-4aee-8411-6778d021f078</t>
+        </is>
+      </c>
+      <c r="B44" s="1" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="C44" s="1" t="n">
+        <v>1.1901063</v>
+      </c>
+      <c r="D44" s="1" t="inlineStr">
+        <is>
+          <t>Abweichung vom Zielwert -12 °C</t>
+        </is>
+      </c>
+      <c r="E44" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>69febfea-93f2-4aee-8411-6778d021f078</t>
+        </is>
+      </c>
+      <c r="B45" s="1" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="C45" s="1" t="n">
+        <v>1.324312746</v>
+      </c>
+      <c r="D45" s="1" t="inlineStr">
+        <is>
+          <t>Abweichung vom Zielwert -12 °C</t>
+        </is>
+      </c>
+      <c r="E45" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="F45" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>69febfea-93f2-4aee-8411-6778d021f078</t>
+        </is>
+      </c>
+      <c r="B46" s="1" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="C46" s="1" t="n">
+        <v>11.05134908984</v>
+      </c>
+      <c r="D46" s="1" t="inlineStr">
+        <is>
+          <t>Abweichung vom Zielwert -12 °C</t>
+        </is>
+      </c>
+      <c r="E46" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F46" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>ee65e316-170a-44d6-9f78-450e8ec54ccf</t>
+        </is>
+      </c>
+      <c r="B47" s="1" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="C47" s="1" t="n">
+        <v>8.096171719999999</v>
+      </c>
+      <c r="D47" s="1" t="inlineStr">
+        <is>
+          <t>Abweichung vom Zielwert -12 °C</t>
+        </is>
+      </c>
+      <c r="E47" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="F47" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>ee65e316-170a-44d6-9f78-450e8ec54ccf</t>
+        </is>
+      </c>
+      <c r="B48" s="1" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="C48" s="1" t="n">
+        <v>7.99693754</v>
+      </c>
+      <c r="D48" s="1" t="inlineStr">
+        <is>
+          <t>Abweichung vom Zielwert -12 °C</t>
+        </is>
+      </c>
+      <c r="E48" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>ee65e316-170a-44d6-9f78-450e8ec54ccf</t>
+        </is>
+      </c>
+      <c r="B49" s="1" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="C49" s="1" t="n">
+        <v>14.78459602</v>
+      </c>
+      <c r="D49" s="1" t="inlineStr">
+        <is>
+          <t>Abweichung vom Zielwert -12 °C</t>
+        </is>
+      </c>
+      <c r="E49" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F49" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>5. Zusammenfassung Rangfolge Zielabweichung</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>Über alle Teilnehmer zusammengefasste Rangordnung der Zielabweichung.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Visualisierung</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Anzahl Teilnehmer</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Mittlerer Rang</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Medianer Rang</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Anzahl beste Methode / Gleichstand</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Anteil beste Methode / Gleichstand</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>Kennzahl</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>Finale Rangordnung</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="B55" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C55" s="1" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="D55" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E55" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F55" s="1" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="G55" s="1" t="inlineStr">
+        <is>
+          <t>Abweichung vom Zielwert -12 °C</t>
+        </is>
+      </c>
+      <c r="H55" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="B56" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C56" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D56" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E56" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F56" s="1" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="G56" s="1" t="inlineStr">
+        <is>
+          <t>Abweichung vom Zielwert -12 °C</t>
+        </is>
+      </c>
+      <c r="H56" s="1" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="B57" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C57" s="1" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="D57" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="E57" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F57" s="1" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="G57" s="1" t="inlineStr">
+        <is>
+          <t>Abweichung vom Zielwert -12 °C</t>
+        </is>
+      </c>
+      <c r="H57" s="1" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60">
+      <c r="A60" s="1" t="inlineStr">
+        <is>
+          <t>6. Rangfolge Antwortzeit pro Teilnehmer</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="inlineStr">
+        <is>
+          <t>Rang 1 entspricht der schnellsten Regionsentscheidung innerhalb derselben Person; dadurch werden Unterschiede zwischen Hardware-/Systemgeschwindigkeiten weniger relevant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Teilnehmer-ID</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Visualisierung</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Ausgangswert</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Kennzahl</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Rang innerhalb Teilnehmer</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>Beste Methode / Gleichstand</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="inlineStr">
+        <is>
+          <t>4d19396b-7d8d-4d99-8da7-ded7bf2ae5ef</t>
+        </is>
+      </c>
+      <c r="B63" s="1" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="C63" s="1" t="n">
+        <v>55819</v>
+      </c>
+      <c r="D63" s="1" t="inlineStr">
+        <is>
+          <t>Antwortzeit</t>
+        </is>
+      </c>
+      <c r="E63" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="F63" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="inlineStr">
+        <is>
+          <t>4d19396b-7d8d-4d99-8da7-ded7bf2ae5ef</t>
+        </is>
+      </c>
+      <c r="B64" s="1" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="C64" s="1" t="n">
+        <v>45428</v>
+      </c>
+      <c r="D64" s="1" t="inlineStr">
+        <is>
+          <t>Antwortzeit</t>
+        </is>
+      </c>
+      <c r="E64" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F64" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="inlineStr">
+        <is>
+          <t>4d19396b-7d8d-4d99-8da7-ded7bf2ae5ef</t>
+        </is>
+      </c>
+      <c r="B65" s="1" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="C65" s="1" t="n">
+        <v>66632</v>
+      </c>
+      <c r="D65" s="1" t="inlineStr">
+        <is>
+          <t>Antwortzeit</t>
+        </is>
+      </c>
+      <c r="E65" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F65" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="inlineStr">
+        <is>
+          <t>69febfea-93f2-4aee-8411-6778d021f078</t>
+        </is>
+      </c>
+      <c r="B66" s="1" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="C66" s="1" t="n">
+        <v>28302</v>
+      </c>
+      <c r="D66" s="1" t="inlineStr">
+        <is>
+          <t>Antwortzeit</t>
+        </is>
+      </c>
+      <c r="E66" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F66" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="inlineStr">
+        <is>
+          <t>69febfea-93f2-4aee-8411-6778d021f078</t>
+        </is>
+      </c>
+      <c r="B67" s="1" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="C67" s="1" t="n">
+        <v>49140</v>
+      </c>
+      <c r="D67" s="1" t="inlineStr">
+        <is>
+          <t>Antwortzeit</t>
+        </is>
+      </c>
+      <c r="E67" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F67" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="inlineStr">
+        <is>
+          <t>69febfea-93f2-4aee-8411-6778d021f078</t>
+        </is>
+      </c>
+      <c r="B68" s="1" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="C68" s="1" t="n">
+        <v>36300</v>
+      </c>
+      <c r="D68" s="1" t="inlineStr">
+        <is>
+          <t>Antwortzeit</t>
+        </is>
+      </c>
+      <c r="E68" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="F68" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="inlineStr">
+        <is>
+          <t>ee65e316-170a-44d6-9f78-450e8ec54ccf</t>
+        </is>
+      </c>
+      <c r="B69" s="1" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="C69" s="1" t="n">
+        <v>71881</v>
+      </c>
+      <c r="D69" s="1" t="inlineStr">
+        <is>
+          <t>Antwortzeit</t>
+        </is>
+      </c>
+      <c r="E69" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F69" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="inlineStr">
+        <is>
+          <t>ee65e316-170a-44d6-9f78-450e8ec54ccf</t>
+        </is>
+      </c>
+      <c r="B70" s="1" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="C70" s="1" t="n">
+        <v>52013</v>
+      </c>
+      <c r="D70" s="1" t="inlineStr">
+        <is>
+          <t>Antwortzeit</t>
+        </is>
+      </c>
+      <c r="E70" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="F70" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="inlineStr">
+        <is>
+          <t>ee65e316-170a-44d6-9f78-450e8ec54ccf</t>
+        </is>
+      </c>
+      <c r="B71" s="1" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="C71" s="1" t="n">
+        <v>43866</v>
+      </c>
+      <c r="D71" s="1" t="inlineStr">
+        <is>
+          <t>Antwortzeit</t>
+        </is>
+      </c>
+      <c r="E71" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F71" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72"/>
+    <row r="73"/>
+    <row r="74">
+      <c r="A74" s="1" t="inlineStr">
+        <is>
+          <t>7. Zusammenfassung Rangfolge Antwortzeit</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="inlineStr">
+        <is>
+          <t>Über alle Teilnehmer zusammengefasste Zeit-Rangordnung der H2-Aufgabe.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Visualisierung</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Anzahl Teilnehmer</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Mittlerer Rang</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Medianer Rang</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>Anzahl beste Methode / Gleichstand</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>Anteil beste Methode / Gleichstand</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>Kennzahl</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>Finale Rangordnung</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="B77" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C77" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D77" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E77" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F77" s="1" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="G77" s="1" t="inlineStr">
+        <is>
+          <t>Antwortzeit</t>
+        </is>
+      </c>
+      <c r="H77" s="1" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="B78" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C78" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D78" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E78" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F78" s="1" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="G78" s="1" t="inlineStr">
+        <is>
+          <t>Antwortzeit</t>
+        </is>
+      </c>
+      <c r="H78" s="1" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="B79" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C79" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D79" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E79" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F79" s="1" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="G79" s="1" t="inlineStr">
+        <is>
+          <t>Antwortzeit</t>
+        </is>
+      </c>
+      <c r="H79" s="1" t="n">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1229,7 +2894,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1522,7 +3187,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1606,7 +3271,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P40"/>
+  <dimension ref="A1:Q40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="75" customWidth="1" min="1" max="1"/>
@@ -1625,6 +3290,7 @@
     <col width="25" customWidth="1" min="14" max="14"/>
     <col width="27" customWidth="1" min="15" max="15"/>
     <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="41" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1715,6 +3381,11 @@
           <t>Exakt</t>
         </is>
       </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>Normalisierte absolute Abweichung</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -1775,6 +3446,9 @@
       <c r="P3" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="Q3" s="1" t="n">
+        <v>0.05018128007253322</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -1835,6 +3509,9 @@
       <c r="P4" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="Q4" s="1" t="n">
+        <v>0.02849560205286446</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -1895,6 +3572,9 @@
       <c r="P5" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="Q5" s="1" t="n">
+        <v>0.4250211686153459</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -1955,6 +3635,9 @@
       <c r="P6" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="Q6" s="1" t="n">
+        <v>3.887133639875507e-06</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -2015,6 +3698,9 @@
       <c r="P7" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="Q7" s="1" t="n">
+        <v>0.001202985392700018</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -2075,6 +3761,9 @@
       <c r="P8" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="Q8" s="1" t="n">
+        <v>0.001045895586040112</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -2135,6 +3824,9 @@
       <c r="P9" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="Q9" s="1" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -2195,6 +3887,9 @@
       <c r="P10" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="Q10" s="1" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -2255,6 +3950,9 @@
       <c r="P11" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="Q11" s="1" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -2315,6 +4013,9 @@
       <c r="P12" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="Q12" s="1" t="n">
+        <v>0.01715947155871342</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -2375,6 +4076,9 @@
       <c r="P13" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="Q13" s="1" t="n">
+        <v>0.01625551764079804</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -2434,6 +4138,9 @@
       </c>
       <c r="P14" s="1" t="b">
         <v>1</v>
+      </c>
+      <c r="Q14" s="1" t="n">
+        <v>0.0004128447547194585</v>
       </c>
     </row>
     <row r="15">
@@ -2453,6 +4160,7 @@
       <c r="N15" s="1" t="inlineStr"/>
       <c r="O15" s="1" t="inlineStr"/>
       <c r="P15" s="1" t="inlineStr"/>
+      <c r="Q15" s="1" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -2513,6 +4221,9 @@
       <c r="P16" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="Q16" s="1" t="n">
+        <v>0.05562323603998522</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -2573,6 +4284,9 @@
       <c r="P17" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="Q17" s="1" t="n">
+        <v>0.1962168778003666</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -2633,6 +4347,9 @@
       <c r="P18" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="Q18" s="1" t="n">
+        <v>0.3781469339181233</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -2693,6 +4410,9 @@
       <c r="P19" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="Q19" s="1" t="n">
+        <v>0.02800267749923755</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -2753,6 +4473,9 @@
       <c r="P20" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="Q20" s="1" t="n">
+        <v>0.0537146564047943</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -2813,6 +4536,9 @@
       <c r="P21" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="Q21" s="1" t="n">
+        <v>0.001214329563811354</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -2873,6 +4599,9 @@
       <c r="P22" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="Q22" s="1" t="n">
+        <v>0.00176094919074602</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -2933,6 +4662,9 @@
       <c r="P23" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="Q23" s="1" t="n">
+        <v>0.02953111792880939</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
@@ -2993,6 +4725,9 @@
       <c r="P24" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="Q24" s="1" t="n">
+        <v>0.002234448862035163</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -3053,6 +4788,9 @@
       <c r="P25" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="Q25" s="1" t="n">
+        <v>0.05168385874839454</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
@@ -3113,6 +4851,9 @@
       <c r="P26" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="Q26" s="1" t="n">
+        <v>0.02986961149547421</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
@@ -3172,6 +4913,9 @@
       </c>
       <c r="P27" s="1" t="b">
         <v>0</v>
+      </c>
+      <c r="Q27" s="1" t="n">
+        <v>0.06525490717841065</v>
       </c>
     </row>
     <row r="28">
@@ -3191,6 +4935,7 @@
       <c r="N28" s="1" t="inlineStr"/>
       <c r="O28" s="1" t="inlineStr"/>
       <c r="P28" s="1" t="inlineStr"/>
+      <c r="Q28" s="1" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
@@ -3251,6 +4996,9 @@
       <c r="P29" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="Q29" s="1" t="n">
+        <v>0.05120713904609903</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
@@ -3311,6 +5059,9 @@
       <c r="P30" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="Q30" s="1" t="n">
+        <v>0.0461288065601473</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
@@ -3371,6 +5122,9 @@
       <c r="P31" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="Q31" s="1" t="n">
+        <v>0.02849560205286446</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
@@ -3431,6 +5185,9 @@
       <c r="P32" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="Q32" s="1" t="n">
+        <v>0.01384066131248256</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
@@ -3491,6 +5248,9 @@
       <c r="P33" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="Q33" s="1" t="n">
+        <v>0.01701043744616513</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
@@ -3551,6 +5311,9 @@
       <c r="P34" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="Q34" s="1" t="n">
+        <v>0.011569278557913</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
@@ -3611,6 +5374,9 @@
       <c r="P35" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="Q35" s="1" t="n">
+        <v>0.00176094919074602</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
@@ -3671,6 +5437,9 @@
       <c r="P36" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="Q36" s="1" t="n">
+        <v>0.008348855774347732</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
@@ -3731,6 +5500,9 @@
       <c r="P37" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="Q37" s="1" t="n">
+        <v>0.003631468553360225</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
@@ -3791,6 +5563,9 @@
       <c r="P38" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="Q38" s="1" t="n">
+        <v>0.07467207212847889</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
@@ -3851,6 +5626,9 @@
       <c r="P39" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="Q39" s="1" t="n">
+        <v>0.01715947155871342</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
@@ -3911,9 +5689,12 @@
       <c r="P40" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="Q40" s="1" t="n">
+        <v>0.07177041918417149</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:P40"/>
+  <autoFilter ref="A2:Q40"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3924,7 +5705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P40"/>
+  <dimension ref="A1:Q40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="75" customWidth="1" min="1" max="1"/>
@@ -3943,6 +5724,7 @@
     <col width="25" customWidth="1" min="14" max="14"/>
     <col width="27" customWidth="1" min="15" max="15"/>
     <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="41" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4033,6 +5815,11 @@
           <t>Exakt</t>
         </is>
       </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>Normalisierte absolute Abweichung</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -4093,6 +5880,9 @@
       <c r="P3" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="Q3" s="1" t="n">
+        <v>0.05018128007253322</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -4153,6 +5943,9 @@
       <c r="P4" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="Q4" s="1" t="n">
+        <v>0.02849560205286446</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -4213,6 +6006,9 @@
       <c r="P5" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="Q5" s="1" t="n">
+        <v>0.4250211686153459</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -4273,6 +6069,9 @@
       <c r="P6" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="Q6" s="1" t="n">
+        <v>3.887133639875507e-06</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -4333,6 +6132,9 @@
       <c r="P7" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="Q7" s="1" t="n">
+        <v>0.001202985392700018</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -4393,6 +6195,9 @@
       <c r="P8" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="Q8" s="1" t="n">
+        <v>0.001045895586040112</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -4453,6 +6258,9 @@
       <c r="P9" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="Q9" s="1" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -4513,6 +6321,9 @@
       <c r="P10" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="Q10" s="1" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -4573,6 +6384,9 @@
       <c r="P11" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="Q11" s="1" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -4633,6 +6447,9 @@
       <c r="P12" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="Q12" s="1" t="n">
+        <v>0.01715947155871342</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -4693,6 +6510,9 @@
       <c r="P13" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="Q13" s="1" t="n">
+        <v>0.01625551764079804</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -4752,6 +6572,9 @@
       </c>
       <c r="P14" s="1" t="b">
         <v>1</v>
+      </c>
+      <c r="Q14" s="1" t="n">
+        <v>0.0004128447547194585</v>
       </c>
     </row>
     <row r="15">
@@ -4771,6 +6594,7 @@
       <c r="N15" s="1" t="inlineStr"/>
       <c r="O15" s="1" t="inlineStr"/>
       <c r="P15" s="1" t="inlineStr"/>
+      <c r="Q15" s="1" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -4831,6 +6655,9 @@
       <c r="P16" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="Q16" s="1" t="n">
+        <v>0.05562323603998522</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -4891,6 +6718,9 @@
       <c r="P17" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="Q17" s="1" t="n">
+        <v>0.1962168778003666</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -4951,6 +6781,9 @@
       <c r="P18" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="Q18" s="1" t="n">
+        <v>0.3781469339181233</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -5011,6 +6844,9 @@
       <c r="P19" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="Q19" s="1" t="n">
+        <v>0.02800267749923755</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -5071,6 +6907,9 @@
       <c r="P20" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="Q20" s="1" t="n">
+        <v>0.0537146564047943</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -5131,6 +6970,9 @@
       <c r="P21" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="Q21" s="1" t="n">
+        <v>0.001214329563811354</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -5191,6 +7033,9 @@
       <c r="P22" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="Q22" s="1" t="n">
+        <v>0.00176094919074602</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -5251,6 +7096,9 @@
       <c r="P23" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="Q23" s="1" t="n">
+        <v>0.02953111792880939</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
@@ -5311,6 +7159,9 @@
       <c r="P24" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="Q24" s="1" t="n">
+        <v>0.002234448862035163</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -5371,6 +7222,9 @@
       <c r="P25" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="Q25" s="1" t="n">
+        <v>0.05168385874839454</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
@@ -5431,6 +7285,9 @@
       <c r="P26" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="Q26" s="1" t="n">
+        <v>0.02986961149547421</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
@@ -5490,6 +7347,9 @@
       </c>
       <c r="P27" s="1" t="b">
         <v>0</v>
+      </c>
+      <c r="Q27" s="1" t="n">
+        <v>0.06525490717841065</v>
       </c>
     </row>
     <row r="28">
@@ -5509,6 +7369,7 @@
       <c r="N28" s="1" t="inlineStr"/>
       <c r="O28" s="1" t="inlineStr"/>
       <c r="P28" s="1" t="inlineStr"/>
+      <c r="Q28" s="1" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
@@ -5569,6 +7430,9 @@
       <c r="P29" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="Q29" s="1" t="n">
+        <v>0.05120713904609903</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
@@ -5629,6 +7493,9 @@
       <c r="P30" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="Q30" s="1" t="n">
+        <v>0.0461288065601473</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
@@ -5689,6 +7556,9 @@
       <c r="P31" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="Q31" s="1" t="n">
+        <v>0.02849560205286446</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
@@ -5749,6 +7619,9 @@
       <c r="P32" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="Q32" s="1" t="n">
+        <v>0.01384066131248256</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
@@ -5809,6 +7682,9 @@
       <c r="P33" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="Q33" s="1" t="n">
+        <v>0.01701043744616513</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
@@ -5869,6 +7745,9 @@
       <c r="P34" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="Q34" s="1" t="n">
+        <v>0.011569278557913</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
@@ -5929,6 +7808,9 @@
       <c r="P35" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="Q35" s="1" t="n">
+        <v>0.00176094919074602</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
@@ -5989,6 +7871,9 @@
       <c r="P36" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="Q36" s="1" t="n">
+        <v>0.008348855774347732</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
@@ -6049,6 +7934,9 @@
       <c r="P37" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="Q37" s="1" t="n">
+        <v>0.003631468553360225</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
@@ -6109,6 +7997,9 @@
       <c r="P38" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="Q38" s="1" t="n">
+        <v>0.07467207212847889</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
@@ -6169,6 +8060,9 @@
       <c r="P39" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="Q39" s="1" t="n">
+        <v>0.01715947155871342</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
@@ -6229,9 +8123,12 @@
       <c r="P40" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="Q40" s="1" t="n">
+        <v>0.07177041918417149</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:P40"/>
+  <autoFilter ref="A2:Q40"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6714,17 +8611,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H57"/>
+  <dimension ref="A1:I57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="75" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="36" customWidth="1" min="3" max="3"/>
-    <col width="35" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="42" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="49" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="7" max="7"/>
     <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6771,15 +8669,25 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>Mittlere normalisierte absolute Abweichung</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Mediane normalisierte absolute Abweichung</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>Mittlere Antwortzeit (ms)</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Anzahl Aufgaben</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>Anteil exakt</t>
         </is>
@@ -6803,12 +8711,18 @@
         <v>1.54667823548e-05</v>
       </c>
       <c r="E5" s="1" t="n">
+        <v>0.1066199772390264</v>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>0.0007293701703797851</v>
+      </c>
+      <c r="G5" s="1" t="n">
         <v>20252.5</v>
       </c>
-      <c r="F5" s="1" t="n">
+      <c r="H5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="G5" s="1" t="n">
+      <c r="I5" s="1" t="n">
         <v>0.75</v>
       </c>
     </row>
@@ -6830,12 +8744,18 @@
         <v>1.078096916799999e-06</v>
       </c>
       <c r="E6" s="1" t="n">
+        <v>0.01148852627159063</v>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>0.008729251516749031</v>
+      </c>
+      <c r="G6" s="1" t="n">
         <v>22607</v>
       </c>
-      <c r="F6" s="1" t="n">
+      <c r="H6" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="G6" s="1" t="n">
+      <c r="I6" s="1" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -6857,12 +8777,18 @@
         <v>1.821786107949999e-06</v>
       </c>
       <c r="E7" s="1" t="n">
+        <v>0.01683615969122163</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>0.008581679346176648</v>
+      </c>
+      <c r="G7" s="1" t="n">
         <v>11801</v>
       </c>
-      <c r="F7" s="1" t="n">
+      <c r="H7" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="G7" s="1" t="n">
+      <c r="I7" s="1" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -6884,12 +8810,18 @@
         <v>5.710013727219127</v>
       </c>
       <c r="E8" s="1" t="n">
+        <v>0.1117126548805951</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>0.03374467802022291</v>
+      </c>
+      <c r="G8" s="1" t="n">
         <v>18598</v>
       </c>
-      <c r="F8" s="1" t="n">
+      <c r="H8" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="G8" s="1" t="n">
+      <c r="I8" s="1" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -6911,12 +8843,18 @@
         <v>75.46500712292151</v>
       </c>
       <c r="E9" s="1" t="n">
+        <v>0.07733306590736114</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>0.04179213395013426</v>
+      </c>
+      <c r="G9" s="1" t="n">
         <v>16844</v>
       </c>
-      <c r="F9" s="1" t="n">
+      <c r="H9" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="G9" s="1" t="n">
+      <c r="I9" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6938,12 +8876,18 @@
         <v>4.500002019195</v>
       </c>
       <c r="E10" s="1" t="n">
+        <v>0.03426768036959083</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>0.03984326812381605</v>
+      </c>
+      <c r="G10" s="1" t="n">
         <v>16513</v>
       </c>
-      <c r="F10" s="1" t="n">
+      <c r="H10" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="G10" s="1" t="n">
+      <c r="I10" s="1" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -6965,12 +8909,18 @@
         <v>9.280001034425835</v>
       </c>
       <c r="E11" s="1" t="n">
+        <v>0.02886669208707729</v>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>0.02003244030538873</v>
+      </c>
+      <c r="G11" s="1" t="n">
         <v>20008.5</v>
       </c>
-      <c r="F11" s="1" t="n">
+      <c r="H11" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="G11" s="1" t="n">
+      <c r="I11" s="1" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -6992,12 +8942,18 @@
         <v>21.33500167453413</v>
       </c>
       <c r="E12" s="1" t="n">
+        <v>0.02216189283484339</v>
+      </c>
+      <c r="F12" s="1" t="n">
+        <v>0.01708495450243928</v>
+      </c>
+      <c r="G12" s="1" t="n">
         <v>18556.5</v>
       </c>
-      <c r="F12" s="1" t="n">
+      <c r="H12" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="G12" s="1" t="n">
+      <c r="I12" s="1" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -7019,12 +8975,18 @@
         <v>4.500001858885</v>
       </c>
       <c r="E13" s="1" t="n">
+        <v>0.03537020541945162</v>
+      </c>
+      <c r="F13" s="1" t="n">
+        <v>0.0325239001792908</v>
+      </c>
+      <c r="G13" s="1" t="n">
         <v>23192</v>
       </c>
-      <c r="F13" s="1" t="n">
+      <c r="H13" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="G13" s="1" t="n">
+      <c r="I13" s="1" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -7040,7 +9002,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>Ergänzende Rangbetrachtung innerhalb derselben Person: Rang 1 entspricht der Methode mit der kleinsten mittleren absoluten Abweichung. Bei Gleichständen werden durchschnittliche Ränge vergeben.</t>
+          <t>Ergänzende Rangbetrachtung innerhalb derselben Person: Rang 1 entspricht der Methode mit der kleinsten mittleren normalisierten absoluten Abweichung. Bei Gleichständen werden durchschnittliche Ränge vergeben.</t>
         </is>
       </c>
     </row>
@@ -7088,15 +9050,15 @@
         </is>
       </c>
       <c r="C19" s="1" t="n">
-        <v>21.92500091089233</v>
+        <v>0.01683615969122163</v>
       </c>
       <c r="D19" s="1" t="inlineStr">
         <is>
-          <t>Genauigkeit</t>
+          <t>Genauigkeit (normalisierte absolute Abweichung)</t>
         </is>
       </c>
       <c r="E19" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F19" s="1" t="b">
         <v>0</v>
@@ -7114,18 +9076,18 @@
         </is>
       </c>
       <c r="C20" s="1" t="n">
-        <v>20.77000053904889</v>
+        <v>0.01148852627159063</v>
       </c>
       <c r="D20" s="1" t="inlineStr">
         <is>
-          <t>Genauigkeit</t>
+          <t>Genauigkeit (normalisierte absolute Abweichung)</t>
         </is>
       </c>
       <c r="E20" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F20" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -7140,18 +9102,18 @@
         </is>
       </c>
       <c r="C21" s="1" t="n">
-        <v>0.527507733391323</v>
+        <v>0.1066199772390264</v>
       </c>
       <c r="D21" s="1" t="inlineStr">
         <is>
-          <t>Genauigkeit</t>
+          <t>Genauigkeit (normalisierte absolute Abweichung)</t>
         </is>
       </c>
       <c r="E21" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F21" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -7166,11 +9128,11 @@
         </is>
       </c>
       <c r="C22" s="1" t="n">
-        <v>68.28750151786265</v>
+        <v>0.03426768036959083</v>
       </c>
       <c r="D22" s="1" t="inlineStr">
         <is>
-          <t>Genauigkeit</t>
+          <t>Genauigkeit (normalisierte absolute Abweichung)</t>
         </is>
       </c>
       <c r="E22" s="1" t="n">
@@ -7192,11 +9154,11 @@
         </is>
       </c>
       <c r="C23" s="1" t="n">
-        <v>75.89750453641354</v>
+        <v>0.07733306590736114</v>
       </c>
       <c r="D23" s="1" t="inlineStr">
         <is>
-          <t>Genauigkeit</t>
+          <t>Genauigkeit (normalisierte absolute Abweichung)</t>
         </is>
       </c>
       <c r="E23" s="1" t="n">
@@ -7218,11 +9180,11 @@
         </is>
       </c>
       <c r="C24" s="1" t="n">
-        <v>86.23250688564912</v>
+        <v>0.1117126548805951</v>
       </c>
       <c r="D24" s="1" t="inlineStr">
         <is>
-          <t>Genauigkeit</t>
+          <t>Genauigkeit (normalisierte absolute Abweichung)</t>
         </is>
       </c>
       <c r="E24" s="1" t="n">
@@ -7244,11 +9206,11 @@
         </is>
       </c>
       <c r="C25" s="1" t="n">
-        <v>97.66000118065926</v>
+        <v>0.03537020541945162</v>
       </c>
       <c r="D25" s="1" t="inlineStr">
         <is>
-          <t>Genauigkeit</t>
+          <t>Genauigkeit (normalisierte absolute Abweichung)</t>
         </is>
       </c>
       <c r="E25" s="1" t="n">
@@ -7270,11 +9232,11 @@
         </is>
       </c>
       <c r="C26" s="1" t="n">
-        <v>32.59250114601672</v>
+        <v>0.02216189283484339</v>
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
-          <t>Genauigkeit</t>
+          <t>Genauigkeit (normalisierte absolute Abweichung)</t>
         </is>
       </c>
       <c r="E26" s="1" t="n">
@@ -7296,11 +9258,11 @@
         </is>
       </c>
       <c r="C27" s="1" t="n">
-        <v>96.34250072720218</v>
+        <v>0.02886669208707729</v>
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
-          <t>Genauigkeit</t>
+          <t>Genauigkeit (normalisierte absolute Abweichung)</t>
         </is>
       </c>
       <c r="E27" s="1" t="n">
@@ -7378,20 +9340,20 @@
         <v>3</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>1.666666666666667</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="D33" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="E33" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="F33" s="1" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="G33" s="1" t="inlineStr">
         <is>
-          <t>Genauigkeit</t>
+          <t>Genauigkeit (normalisierte absolute Abweichung)</t>
         </is>
       </c>
       <c r="H33" s="1" t="n">
@@ -7401,7 +9363,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>IsoGlyph</t>
+          <t>VSUP</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
@@ -7421,7 +9383,7 @@
       </c>
       <c r="G34" s="1" t="inlineStr">
         <is>
-          <t>Genauigkeit</t>
+          <t>Genauigkeit (normalisierte absolute Abweichung)</t>
         </is>
       </c>
       <c r="H34" s="1" t="n">
@@ -7431,27 +9393,27 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>VSUP</t>
+          <t>IsoGlyph</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
         <v>3</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>2.333333333333333</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="D35" s="1" t="n">
         <v>3</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="G35" s="1" t="inlineStr">
         <is>
-          <t>Genauigkeit</t>
+          <t>Genauigkeit (normalisierte absolute Abweichung)</t>
         </is>
       </c>
       <c r="H35" s="1" t="n">
@@ -7915,7 +9877,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Statistischer Entscheidungsweg für die H1-Genauigkeit.</t>
+          <t>Statistischer Entscheidungsweg für die H1-Genauigkeit auf Basis der normalisierten absoluten Abweichung, damit Luftdruck und Niederschlag gleichgewichtet vergleichbar sind.</t>
         </is>
       </c>
     </row>
@@ -7970,10 +9932,10 @@
         <v>3</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>0.8389793358986353</v>
+        <v>0.8524414943261528</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>0.2114055277419913</v>
+        <v>0.2470015276064622</v>
       </c>
       <c r="E5" s="1" t="b">
         <v>1</v>
@@ -7989,10 +9951,10 @@
         <v>3</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>0.9998561022581308</v>
+        <v>0.8443327893362765</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>0.9770892775941569</v>
+        <v>0.2254095077394547</v>
       </c>
       <c r="E6" s="1" t="b">
         <v>1</v>
@@ -8008,10 +9970,10 @@
         <v>3</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>0.9759495949079769</v>
+        <v>0.9554375741204306</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>0.7026150677187408</v>
+        <v>0.5937762009135443</v>
       </c>
       <c r="E7" s="1" t="b">
         <v>1</v>
@@ -8080,7 +10042,7 @@
         <v>3</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>0.5623690250948515</v>
+        <v>2.621748762064472</v>
       </c>
       <c r="D13" s="1" t="inlineStr">
         <is>
@@ -8088,7 +10050,7 @@
         </is>
       </c>
       <c r="E13" s="1" t="n">
-        <v>0.6092234894264154</v>
+        <v>0.1872609939394737</v>
       </c>
       <c r="F13" s="1" t="b">
         <v>0</v>
@@ -8485,16 +10447,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L73"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="75" customWidth="1" min="1" max="1"/>
     <col width="29" customWidth="1" min="2" max="2"/>
     <col width="38" customWidth="1" min="3" max="3"/>
-    <col width="41" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="42" customWidth="1" min="6" max="6"/>
-    <col width="41" customWidth="1" min="7" max="7"/>
+    <col width="37" customWidth="1" min="4" max="4"/>
+    <col width="31" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
     <col width="37" customWidth="1" min="8" max="8"/>
     <col width="33" customWidth="1" min="9" max="9"/>
     <col width="32" customWidth="1" min="10" max="10"/>
@@ -8505,1497 +10467,194 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Absolute H2-Ergebnisse und direkt anschließend ergänzende Within-Participant-Rangfolgen für Unsicherheit, Zielabweichung und Antwortzeit.</t>
+          <t>Deskriptive Zusammenfassung der H2-Regionsentscheidungen je Visualisierung. Die ergänzenden Within-Participant-Rangfolgen stehen analog zu H1 im Blatt 'H2 Teilnehmer Methoden'.</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>1. Absolute/deskriptive Werte nach Methode</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Visualisierung</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Anzahl Entscheidungen</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Mittlere gewählte Unsicherheit</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Mediane gewählte Unsicherheit</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Mittlere Zielabweichung</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Mediane Zielabweichung</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Mittlere subjektive Sicherheit</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Mediane subjektive Sicherheit</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Mittlere Antwortzeit (ms)</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Mediane Antwortzeit (ms)</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Anteil sicherste Region gewählt</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Auswertbare Entscheidungen</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Zusammenfassung der tatsächlich gewählten Regionen und ihrer Unsicherheit, Zielabweichung, subjektiven Sicherheit und Antwortzeit.</t>
-        </is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>1.7319748712</v>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>1.424277884</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>11.41034957261333</v>
+      </c>
+      <c r="F3" s="1" t="n">
+        <v>11.05134908984</v>
+      </c>
+      <c r="G3" s="1" t="n">
+        <v>5.666666666666667</v>
+      </c>
+      <c r="H3" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="I3" s="1" t="n">
+        <v>48932.66666666666</v>
+      </c>
+      <c r="J3" s="1" t="n">
+        <v>43866</v>
+      </c>
+      <c r="K3" s="1" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="L3" s="1" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Visualisierung</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Anzahl Entscheidungen</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Mittlere gewählte Unsicherheit</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Mediane gewählte Unsicherheit</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Mittlere Zielabweichung</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Mediane Zielabweichung</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Mittlere subjektive Sicherheit</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Mediane subjektive Sicherheit</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Mittlere Antwortzeit (ms)</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>Mediane Antwortzeit (ms)</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>Anteil sicherste Region gewählt</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>Auswertbare Entscheidungen</t>
-        </is>
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>3.19965337</v>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>3.080212368</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>6.806759380933333</v>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>7.99693754</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="H4" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="I4" s="1" t="n">
+        <v>48860.33333333334</v>
+      </c>
+      <c r="J4" s="1" t="n">
+        <v>49140</v>
+      </c>
+      <c r="K4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="1" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>IsoGlyph</t>
+          <t>VSUP</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>1.7319748712</v>
+        <v>3.333614046666666</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>1.424277884</v>
+        <v>3.135608284</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>11.41034957261333</v>
+        <v>6.682401515306666</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>11.05134908984</v>
+        <v>8.096171719999999</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>5.666666666666667</v>
+        <v>5.333333333333333</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>48932.66666666666</v>
+        <v>52000.66666666666</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>43866</v>
+        <v>55819</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="L5" s="1" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>ScaledGlyph</t>
-        </is>
-      </c>
-      <c r="B6" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="C6" s="1" t="n">
-        <v>3.19965337</v>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>3.080212368</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>6.806759380933333</v>
-      </c>
-      <c r="F6" s="1" t="n">
-        <v>7.99693754</v>
-      </c>
-      <c r="G6" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="H6" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="I6" s="1" t="n">
-        <v>48860.33333333334</v>
-      </c>
-      <c r="J6" s="1" t="n">
-        <v>49140</v>
-      </c>
-      <c r="K6" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="1" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>VSUP</t>
-        </is>
-      </c>
-      <c r="B7" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="C7" s="1" t="n">
-        <v>3.333614046666666</v>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>3.135608284</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>6.682401515306666</v>
-      </c>
-      <c r="F7" s="1" t="n">
-        <v>8.096171719999999</v>
-      </c>
-      <c r="G7" s="1" t="n">
-        <v>5.333333333333333</v>
-      </c>
-      <c r="H7" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="I7" s="1" t="n">
-        <v>52000.66666666666</v>
-      </c>
-      <c r="J7" s="1" t="n">
-        <v>55819</v>
-      </c>
-      <c r="K7" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="1" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8"/>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>2. Rangfolge Unsicherheit pro Teilnehmer</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>Rang 1 entspricht innerhalb derselben Person der Methode, unter der die Region mit der geringsten Unsicherheit gewählt wurde.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Teilnehmer-ID</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Visualisierung</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Ausgangswert</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Kennzahl</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Rang innerhalb Teilnehmer</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Beste Methode / Gleichstand</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>4d19396b-7d8d-4d99-8da7-ded7bf2ae5ef</t>
-        </is>
-      </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>VSUP</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="n">
-        <v>3.135608284</v>
-      </c>
-      <c r="D13" s="1" t="inlineStr">
-        <is>
-          <t>Unsicherheit der gewählten Region</t>
-        </is>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="F13" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>4d19396b-7d8d-4d99-8da7-ded7bf2ae5ef</t>
-        </is>
-      </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>ScaledGlyph</t>
-        </is>
-      </c>
-      <c r="C14" s="1" t="n">
-        <v>3.080212368</v>
-      </c>
-      <c r="D14" s="1" t="inlineStr">
-        <is>
-          <t>Unsicherheit der gewählten Region</t>
-        </is>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="F14" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>4d19396b-7d8d-4d99-8da7-ded7bf2ae5ef</t>
-        </is>
-      </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>IsoGlyph</t>
-        </is>
-      </c>
-      <c r="C15" s="1" t="n">
-        <v>1.424277884</v>
-      </c>
-      <c r="D15" s="1" t="inlineStr">
-        <is>
-          <t>Unsicherheit der gewählten Region</t>
-        </is>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>69febfea-93f2-4aee-8411-6778d021f078</t>
-        </is>
-      </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>VSUP</t>
-        </is>
-      </c>
-      <c r="C16" s="1" t="n">
-        <v>5.4355829</v>
-      </c>
-      <c r="D16" s="1" t="inlineStr">
-        <is>
-          <t>Unsicherheit der gewählten Region</t>
-        </is>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="F16" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>69febfea-93f2-4aee-8411-6778d021f078</t>
-        </is>
-      </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>ScaledGlyph</t>
-        </is>
-      </c>
-      <c r="C17" s="1" t="n">
-        <v>5.06290306</v>
-      </c>
-      <c r="D17" s="1" t="inlineStr">
-        <is>
-          <t>Unsicherheit der gewählten Region</t>
-        </is>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="F17" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>69febfea-93f2-4aee-8411-6778d021f078</t>
-        </is>
-      </c>
-      <c r="B18" s="1" t="inlineStr">
-        <is>
-          <t>IsoGlyph</t>
-        </is>
-      </c>
-      <c r="C18" s="1" t="n">
-        <v>3.129501516</v>
-      </c>
-      <c r="D18" s="1" t="inlineStr">
-        <is>
-          <t>Unsicherheit der gewählten Region</t>
-        </is>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>ee65e316-170a-44d6-9f78-450e8ec54ccf</t>
-        </is>
-      </c>
-      <c r="B19" s="1" t="inlineStr">
-        <is>
-          <t>VSUP</t>
-        </is>
-      </c>
-      <c r="C19" s="1" t="n">
-        <v>1.429650956</v>
-      </c>
-      <c r="D19" s="1" t="inlineStr">
-        <is>
-          <t>Unsicherheit der gewählten Region</t>
-        </is>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="F19" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>ee65e316-170a-44d6-9f78-450e8ec54ccf</t>
-        </is>
-      </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>ScaledGlyph</t>
-        </is>
-      </c>
-      <c r="C20" s="1" t="n">
-        <v>1.455844682</v>
-      </c>
-      <c r="D20" s="1" t="inlineStr">
-        <is>
-          <t>Unsicherheit der gewählten Region</t>
-        </is>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="F20" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>ee65e316-170a-44d6-9f78-450e8ec54ccf</t>
-        </is>
-      </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>IsoGlyph</t>
-        </is>
-      </c>
-      <c r="C21" s="1" t="n">
-        <v>0.6421452136</v>
-      </c>
-      <c r="D21" s="1" t="inlineStr">
-        <is>
-          <t>Unsicherheit der gewählten Region</t>
-        </is>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>3. Zusammenfassung Rangfolge Unsicherheit</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>Über alle Teilnehmer zusammengefasste Rangordnung der gewählten Unsicherheit.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>Visualisierung</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>Anzahl Teilnehmer</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Mittlerer Rang</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>Medianer Rang</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Anzahl beste Methode / Gleichstand</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Anteil beste Methode / Gleichstand</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>Kennzahl</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>Finale Rangordnung</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>IsoGlyph</t>
-        </is>
-      </c>
-      <c r="B27" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="C27" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="E27" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="F27" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" s="1" t="inlineStr">
-        <is>
-          <t>Unsicherheit der gewählten Region</t>
-        </is>
-      </c>
-      <c r="H27" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>ScaledGlyph</t>
-        </is>
-      </c>
-      <c r="B28" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="C28" s="1" t="n">
-        <v>2.333333333333333</v>
-      </c>
-      <c r="D28" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E28" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" s="1" t="inlineStr">
-        <is>
-          <t>Unsicherheit der gewählten Region</t>
-        </is>
-      </c>
-      <c r="H28" s="1" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>VSUP</t>
-        </is>
-      </c>
-      <c r="B29" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="C29" s="1" t="n">
-        <v>2.666666666666667</v>
-      </c>
-      <c r="D29" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="E29" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" s="1" t="inlineStr">
-        <is>
-          <t>Unsicherheit der gewählten Region</t>
-        </is>
-      </c>
-      <c r="H29" s="1" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>4. Rangfolge Zielabweichung pro Teilnehmer</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr">
-        <is>
-          <t>Rang 1 entspricht der Methode mit der kleinsten Abweichung der gewählten Region vom Zielwert -12 °C.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>Teilnehmer-ID</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>Visualisierung</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Ausgangswert</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>Kennzahl</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>Rang innerhalb Teilnehmer</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>Beste Methode / Gleichstand</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>4d19396b-7d8d-4d99-8da7-ded7bf2ae5ef</t>
-        </is>
-      </c>
-      <c r="B35" s="1" t="inlineStr">
-        <is>
-          <t>VSUP</t>
-        </is>
-      </c>
-      <c r="C35" s="1" t="n">
-        <v>10.76092652592</v>
-      </c>
-      <c r="D35" s="1" t="inlineStr">
-        <is>
-          <t>Abweichung vom Zielwert -12 °C</t>
-        </is>
-      </c>
-      <c r="E35" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="F35" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>4d19396b-7d8d-4d99-8da7-ded7bf2ae5ef</t>
-        </is>
-      </c>
-      <c r="B36" s="1" t="inlineStr">
-        <is>
-          <t>ScaledGlyph</t>
-        </is>
-      </c>
-      <c r="C36" s="1" t="n">
-        <v>11.0990278568</v>
-      </c>
-      <c r="D36" s="1" t="inlineStr">
-        <is>
-          <t>Abweichung vom Zielwert -12 °C</t>
-        </is>
-      </c>
-      <c r="E36" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="F36" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t>4d19396b-7d8d-4d99-8da7-ded7bf2ae5ef</t>
-        </is>
-      </c>
-      <c r="B37" s="1" t="inlineStr">
-        <is>
-          <t>IsoGlyph</t>
-        </is>
-      </c>
-      <c r="C37" s="1" t="n">
-        <v>8.395103607999999</v>
-      </c>
-      <c r="D37" s="1" t="inlineStr">
-        <is>
-          <t>Abweichung vom Zielwert -12 °C</t>
-        </is>
-      </c>
-      <c r="E37" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F37" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>69febfea-93f2-4aee-8411-6778d021f078</t>
-        </is>
-      </c>
-      <c r="B38" s="1" t="inlineStr">
-        <is>
-          <t>VSUP</t>
-        </is>
-      </c>
-      <c r="C38" s="1" t="n">
-        <v>1.1901063</v>
-      </c>
-      <c r="D38" s="1" t="inlineStr">
-        <is>
-          <t>Abweichung vom Zielwert -12 °C</t>
-        </is>
-      </c>
-      <c r="E38" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F38" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>69febfea-93f2-4aee-8411-6778d021f078</t>
-        </is>
-      </c>
-      <c r="B39" s="1" t="inlineStr">
-        <is>
-          <t>ScaledGlyph</t>
-        </is>
-      </c>
-      <c r="C39" s="1" t="n">
-        <v>1.324312746</v>
-      </c>
-      <c r="D39" s="1" t="inlineStr">
-        <is>
-          <t>Abweichung vom Zielwert -12 °C</t>
-        </is>
-      </c>
-      <c r="E39" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="F39" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>69febfea-93f2-4aee-8411-6778d021f078</t>
-        </is>
-      </c>
-      <c r="B40" s="1" t="inlineStr">
-        <is>
-          <t>IsoGlyph</t>
-        </is>
-      </c>
-      <c r="C40" s="1" t="n">
-        <v>11.05134908984</v>
-      </c>
-      <c r="D40" s="1" t="inlineStr">
-        <is>
-          <t>Abweichung vom Zielwert -12 °C</t>
-        </is>
-      </c>
-      <c r="E40" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="F40" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>ee65e316-170a-44d6-9f78-450e8ec54ccf</t>
-        </is>
-      </c>
-      <c r="B41" s="1" t="inlineStr">
-        <is>
-          <t>VSUP</t>
-        </is>
-      </c>
-      <c r="C41" s="1" t="n">
-        <v>8.096171719999999</v>
-      </c>
-      <c r="D41" s="1" t="inlineStr">
-        <is>
-          <t>Abweichung vom Zielwert -12 °C</t>
-        </is>
-      </c>
-      <c r="E41" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="F41" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="inlineStr">
-        <is>
-          <t>ee65e316-170a-44d6-9f78-450e8ec54ccf</t>
-        </is>
-      </c>
-      <c r="B42" s="1" t="inlineStr">
-        <is>
-          <t>ScaledGlyph</t>
-        </is>
-      </c>
-      <c r="C42" s="1" t="n">
-        <v>7.99693754</v>
-      </c>
-      <c r="D42" s="1" t="inlineStr">
-        <is>
-          <t>Abweichung vom Zielwert -12 °C</t>
-        </is>
-      </c>
-      <c r="E42" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F42" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="inlineStr">
-        <is>
-          <t>ee65e316-170a-44d6-9f78-450e8ec54ccf</t>
-        </is>
-      </c>
-      <c r="B43" s="1" t="inlineStr">
-        <is>
-          <t>IsoGlyph</t>
-        </is>
-      </c>
-      <c r="C43" s="1" t="n">
-        <v>14.78459602</v>
-      </c>
-      <c r="D43" s="1" t="inlineStr">
-        <is>
-          <t>Abweichung vom Zielwert -12 °C</t>
-        </is>
-      </c>
-      <c r="E43" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="F43" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46">
-      <c r="A46" s="1" t="inlineStr">
-        <is>
-          <t>5. Zusammenfassung Rangfolge Zielabweichung</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="1" t="inlineStr">
-        <is>
-          <t>Über alle Teilnehmer zusammengefasste Rangordnung der Zielabweichung.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>Visualisierung</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>Anzahl Teilnehmer</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>Mittlerer Rang</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>Medianer Rang</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>Anzahl beste Methode / Gleichstand</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>Anteil beste Methode / Gleichstand</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>Kennzahl</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>Finale Rangordnung</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="inlineStr">
-        <is>
-          <t>VSUP</t>
-        </is>
-      </c>
-      <c r="B49" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="C49" s="1" t="n">
-        <v>1.666666666666667</v>
-      </c>
-      <c r="D49" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E49" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F49" s="1" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="G49" s="1" t="inlineStr">
-        <is>
-          <t>Abweichung vom Zielwert -12 °C</t>
-        </is>
-      </c>
-      <c r="H49" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="inlineStr">
-        <is>
-          <t>ScaledGlyph</t>
-        </is>
-      </c>
-      <c r="B50" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="C50" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="D50" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E50" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F50" s="1" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="G50" s="1" t="inlineStr">
-        <is>
-          <t>Abweichung vom Zielwert -12 °C</t>
-        </is>
-      </c>
-      <c r="H50" s="1" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="inlineStr">
-        <is>
-          <t>IsoGlyph</t>
-        </is>
-      </c>
-      <c r="B51" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="C51" s="1" t="n">
-        <v>2.333333333333333</v>
-      </c>
-      <c r="D51" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="E51" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F51" s="1" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="G51" s="1" t="inlineStr">
-        <is>
-          <t>Abweichung vom Zielwert -12 °C</t>
-        </is>
-      </c>
-      <c r="H51" s="1" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54">
-      <c r="A54" s="1" t="inlineStr">
-        <is>
-          <t>6. Rangfolge Antwortzeit pro Teilnehmer</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="1" t="inlineStr">
-        <is>
-          <t>Rang 1 entspricht der schnellsten Regionsentscheidung innerhalb derselben Person; dadurch werden Unterschiede zwischen den Hardware-/Systemgeschwindigkeiten weniger relevant.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>Teilnehmer-ID</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>Visualisierung</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>Ausgangswert</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>Kennzahl</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>Rang innerhalb Teilnehmer</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>Beste Methode / Gleichstand</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="1" t="inlineStr">
-        <is>
-          <t>4d19396b-7d8d-4d99-8da7-ded7bf2ae5ef</t>
-        </is>
-      </c>
-      <c r="B57" s="1" t="inlineStr">
-        <is>
-          <t>VSUP</t>
-        </is>
-      </c>
-      <c r="C57" s="1" t="n">
-        <v>55819</v>
-      </c>
-      <c r="D57" s="1" t="inlineStr">
-        <is>
-          <t>Antwortzeit</t>
-        </is>
-      </c>
-      <c r="E57" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="F57" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="1" t="inlineStr">
-        <is>
-          <t>4d19396b-7d8d-4d99-8da7-ded7bf2ae5ef</t>
-        </is>
-      </c>
-      <c r="B58" s="1" t="inlineStr">
-        <is>
-          <t>ScaledGlyph</t>
-        </is>
-      </c>
-      <c r="C58" s="1" t="n">
-        <v>45428</v>
-      </c>
-      <c r="D58" s="1" t="inlineStr">
-        <is>
-          <t>Antwortzeit</t>
-        </is>
-      </c>
-      <c r="E58" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F58" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="1" t="inlineStr">
-        <is>
-          <t>4d19396b-7d8d-4d99-8da7-ded7bf2ae5ef</t>
-        </is>
-      </c>
-      <c r="B59" s="1" t="inlineStr">
-        <is>
-          <t>IsoGlyph</t>
-        </is>
-      </c>
-      <c r="C59" s="1" t="n">
-        <v>66632</v>
-      </c>
-      <c r="D59" s="1" t="inlineStr">
-        <is>
-          <t>Antwortzeit</t>
-        </is>
-      </c>
-      <c r="E59" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="F59" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="1" t="inlineStr">
-        <is>
-          <t>69febfea-93f2-4aee-8411-6778d021f078</t>
-        </is>
-      </c>
-      <c r="B60" s="1" t="inlineStr">
-        <is>
-          <t>VSUP</t>
-        </is>
-      </c>
-      <c r="C60" s="1" t="n">
-        <v>28302</v>
-      </c>
-      <c r="D60" s="1" t="inlineStr">
-        <is>
-          <t>Antwortzeit</t>
-        </is>
-      </c>
-      <c r="E60" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F60" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="1" t="inlineStr">
-        <is>
-          <t>69febfea-93f2-4aee-8411-6778d021f078</t>
-        </is>
-      </c>
-      <c r="B61" s="1" t="inlineStr">
-        <is>
-          <t>ScaledGlyph</t>
-        </is>
-      </c>
-      <c r="C61" s="1" t="n">
-        <v>49140</v>
-      </c>
-      <c r="D61" s="1" t="inlineStr">
-        <is>
-          <t>Antwortzeit</t>
-        </is>
-      </c>
-      <c r="E61" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="F61" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="1" t="inlineStr">
-        <is>
-          <t>69febfea-93f2-4aee-8411-6778d021f078</t>
-        </is>
-      </c>
-      <c r="B62" s="1" t="inlineStr">
-        <is>
-          <t>IsoGlyph</t>
-        </is>
-      </c>
-      <c r="C62" s="1" t="n">
-        <v>36300</v>
-      </c>
-      <c r="D62" s="1" t="inlineStr">
-        <is>
-          <t>Antwortzeit</t>
-        </is>
-      </c>
-      <c r="E62" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="F62" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="1" t="inlineStr">
-        <is>
-          <t>ee65e316-170a-44d6-9f78-450e8ec54ccf</t>
-        </is>
-      </c>
-      <c r="B63" s="1" t="inlineStr">
-        <is>
-          <t>VSUP</t>
-        </is>
-      </c>
-      <c r="C63" s="1" t="n">
-        <v>71881</v>
-      </c>
-      <c r="D63" s="1" t="inlineStr">
-        <is>
-          <t>Antwortzeit</t>
-        </is>
-      </c>
-      <c r="E63" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="F63" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="1" t="inlineStr">
-        <is>
-          <t>ee65e316-170a-44d6-9f78-450e8ec54ccf</t>
-        </is>
-      </c>
-      <c r="B64" s="1" t="inlineStr">
-        <is>
-          <t>ScaledGlyph</t>
-        </is>
-      </c>
-      <c r="C64" s="1" t="n">
-        <v>52013</v>
-      </c>
-      <c r="D64" s="1" t="inlineStr">
-        <is>
-          <t>Antwortzeit</t>
-        </is>
-      </c>
-      <c r="E64" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="F64" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="1" t="inlineStr">
-        <is>
-          <t>ee65e316-170a-44d6-9f78-450e8ec54ccf</t>
-        </is>
-      </c>
-      <c r="B65" s="1" t="inlineStr">
-        <is>
-          <t>IsoGlyph</t>
-        </is>
-      </c>
-      <c r="C65" s="1" t="n">
-        <v>43866</v>
-      </c>
-      <c r="D65" s="1" t="inlineStr">
-        <is>
-          <t>Antwortzeit</t>
-        </is>
-      </c>
-      <c r="E65" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F65" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68">
-      <c r="A68" s="1" t="inlineStr">
-        <is>
-          <t>7. Zusammenfassung Rangfolge Antwortzeit</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="1" t="inlineStr">
-        <is>
-          <t>Über alle Teilnehmer zusammengefasste Zeit-Rangordnung der H2-Aufgabe.</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>Visualisierung</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>Anzahl Teilnehmer</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>Mittlerer Rang</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>Medianer Rang</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>Anzahl beste Methode / Gleichstand</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>Anteil beste Methode / Gleichstand</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t>Kennzahl</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>Finale Rangordnung</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="1" t="inlineStr">
-        <is>
-          <t>VSUP</t>
-        </is>
-      </c>
-      <c r="B71" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="C71" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="D71" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E71" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F71" s="1" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="G71" s="1" t="inlineStr">
-        <is>
-          <t>Antwortzeit</t>
-        </is>
-      </c>
-      <c r="H71" s="1" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="1" t="inlineStr">
-        <is>
-          <t>ScaledGlyph</t>
-        </is>
-      </c>
-      <c r="B72" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="C72" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="D72" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E72" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F72" s="1" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="G72" s="1" t="inlineStr">
-        <is>
-          <t>Antwortzeit</t>
-        </is>
-      </c>
-      <c r="H72" s="1" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="1" t="inlineStr">
-        <is>
-          <t>IsoGlyph</t>
-        </is>
-      </c>
-      <c r="B73" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="C73" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="D73" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E73" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F73" s="1" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="G73" s="1" t="inlineStr">
-        <is>
-          <t>Antwortzeit</t>
-        </is>
-      </c>
-      <c r="H73" s="1" t="n">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
+  <autoFilter ref="A2:L5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10006,7 +10665,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="75" customWidth="1" min="1" max="1"/>
@@ -10222,49 +10881,17 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>69febfea-93f2-4aee-8411-6778d021f078</t>
-        </is>
-      </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>VSUP</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="inlineStr">
-        <is>
-          <t>Passendste Temperatur</t>
-        </is>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="F6" s="1" t="n">
-        <v>28302</v>
-      </c>
-      <c r="G6" s="1" t="inlineStr">
-        <is>
-          <t>Temperatur_Regions_VSUP</t>
-        </is>
-      </c>
-      <c r="H6" s="1" t="n">
-        <v>-13.1901063</v>
-      </c>
-      <c r="I6" s="1" t="n">
-        <v>1.1901063</v>
-      </c>
-      <c r="J6" s="1" t="n">
-        <v>5.4355829</v>
-      </c>
-      <c r="K6" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="A6" s="1" t="inlineStr"/>
+      <c r="B6" s="1" t="inlineStr"/>
+      <c r="C6" s="1" t="inlineStr"/>
+      <c r="D6" s="1" t="inlineStr"/>
+      <c r="E6" s="1" t="inlineStr"/>
+      <c r="F6" s="1" t="inlineStr"/>
+      <c r="G6" s="1" t="inlineStr"/>
+      <c r="H6" s="1" t="inlineStr"/>
+      <c r="I6" s="1" t="inlineStr"/>
+      <c r="J6" s="1" t="inlineStr"/>
+      <c r="K6" s="1" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -10274,7 +10901,7 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>ScaledGlyph</t>
+          <t>VSUP</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">
@@ -10284,28 +10911,28 @@
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>Ideale Temperatur von -12 Grad</t>
+          <t>Passendste Temperatur</t>
         </is>
       </c>
       <c r="E7" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>49140</v>
+        <v>28302</v>
       </c>
       <c r="G7" s="1" t="inlineStr">
         <is>
-          <t>Temperatur_Regions_ScaledGlyph</t>
+          <t>Temperatur_Regions_VSUP</t>
         </is>
       </c>
       <c r="H7" s="1" t="n">
-        <v>-13.324312746</v>
+        <v>-13.1901063</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>1.324312746</v>
+        <v>1.1901063</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>5.06290306</v>
+        <v>5.4355829</v>
       </c>
       <c r="K7" s="1" t="b">
         <v>0</v>
@@ -10319,38 +10946,38 @@
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>IsoGlyph</t>
+          <t>ScaledGlyph</t>
         </is>
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
-          <t>Konstante Temperatur und Unsicherheit</t>
+          <t>Ideale Temperatur von -12 Grad</t>
         </is>
       </c>
       <c r="E8" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>36300</v>
+        <v>49140</v>
       </c>
       <c r="G8" s="1" t="inlineStr">
         <is>
-          <t>Temperatur_Regions_IsoGlyph</t>
+          <t>Temperatur_Regions_ScaledGlyph</t>
         </is>
       </c>
       <c r="H8" s="1" t="n">
-        <v>-0.94865091016</v>
+        <v>-13.324312746</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>11.05134908984</v>
+        <v>1.324312746</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>3.129501516</v>
+        <v>5.06290306</v>
       </c>
       <c r="K8" s="1" t="b">
         <v>0</v>
@@ -10359,92 +10986,60 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>ee65e316-170a-44d6-9f78-450e8ec54ccf</t>
+          <t>69febfea-93f2-4aee-8411-6778d021f078</t>
         </is>
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>VSUP</t>
+          <t>IsoGlyph</t>
         </is>
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>Sichere Region mit guten Werten</t>
+          <t>Konstante Temperatur und Unsicherheit</t>
         </is>
       </c>
       <c r="E9" s="1" t="n">
         <v>6</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>71881</v>
+        <v>36300</v>
       </c>
       <c r="G9" s="1" t="inlineStr">
         <is>
-          <t>Temperatur_Regions_VSUP</t>
+          <t>Temperatur_Regions_IsoGlyph</t>
         </is>
       </c>
       <c r="H9" s="1" t="n">
-        <v>-20.09617172</v>
+        <v>-0.94865091016</v>
       </c>
       <c r="I9" s="1" t="n">
-        <v>8.096171719999999</v>
+        <v>11.05134908984</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>1.429650956</v>
+        <v>3.129501516</v>
       </c>
       <c r="K9" s="1" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>ee65e316-170a-44d6-9f78-450e8ec54ccf</t>
-        </is>
-      </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>ScaledGlyph</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>R4</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="inlineStr">
-        <is>
-          <t>Insgesamt die sicherste Region</t>
-        </is>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="F10" s="1" t="n">
-        <v>52013</v>
-      </c>
-      <c r="G10" s="1" t="inlineStr">
-        <is>
-          <t>Temperatur_Regions_ScaledGlyph</t>
-        </is>
-      </c>
-      <c r="H10" s="1" t="n">
-        <v>-19.99693754</v>
-      </c>
-      <c r="I10" s="1" t="n">
-        <v>7.99693754</v>
-      </c>
-      <c r="J10" s="1" t="n">
-        <v>1.455844682</v>
-      </c>
-      <c r="K10" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="A10" s="1" t="inlineStr"/>
+      <c r="B10" s="1" t="inlineStr"/>
+      <c r="C10" s="1" t="inlineStr"/>
+      <c r="D10" s="1" t="inlineStr"/>
+      <c r="E10" s="1" t="inlineStr"/>
+      <c r="F10" s="1" t="inlineStr"/>
+      <c r="G10" s="1" t="inlineStr"/>
+      <c r="H10" s="1" t="inlineStr"/>
+      <c r="I10" s="1" t="inlineStr"/>
+      <c r="J10" s="1" t="inlineStr"/>
+      <c r="K10" s="1" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -10454,45 +11049,135 @@
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="inlineStr">
+        <is>
+          <t>Sichere Region mit guten Werten</t>
+        </is>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>71881</v>
+      </c>
+      <c r="G11" s="1" t="inlineStr">
+        <is>
+          <t>Temperatur_Regions_VSUP</t>
+        </is>
+      </c>
+      <c r="H11" s="1" t="n">
+        <v>-20.09617172</v>
+      </c>
+      <c r="I11" s="1" t="n">
+        <v>8.096171719999999</v>
+      </c>
+      <c r="J11" s="1" t="n">
+        <v>1.429650956</v>
+      </c>
+      <c r="K11" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>ee65e316-170a-44d6-9f78-450e8ec54ccf</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="inlineStr">
+        <is>
+          <t>Insgesamt die sicherste Region</t>
+        </is>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="F12" s="1" t="n">
+        <v>52013</v>
+      </c>
+      <c r="G12" s="1" t="inlineStr">
+        <is>
+          <t>Temperatur_Regions_ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="H12" s="1" t="n">
+        <v>-19.99693754</v>
+      </c>
+      <c r="I12" s="1" t="n">
+        <v>7.99693754</v>
+      </c>
+      <c r="J12" s="1" t="n">
+        <v>1.455844682</v>
+      </c>
+      <c r="K12" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>ee65e316-170a-44d6-9f78-450e8ec54ccf</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
           <t>IsoGlyph</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C13" s="1" t="inlineStr">
         <is>
           <t>R5</t>
         </is>
       </c>
-      <c r="D11" s="1" t="inlineStr">
+      <c r="D13" s="1" t="inlineStr">
         <is>
           <t>Aufgrund der geringen Unsicherheit die vorhersehbarste Region</t>
         </is>
       </c>
-      <c r="E11" s="1" t="n">
+      <c r="E13" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="F11" s="1" t="n">
+      <c r="F13" s="1" t="n">
         <v>43866</v>
       </c>
-      <c r="G11" s="1" t="inlineStr">
+      <c r="G13" s="1" t="inlineStr">
         <is>
           <t>Temperatur_Regions_IsoGlyph</t>
         </is>
       </c>
-      <c r="H11" s="1" t="n">
+      <c r="H13" s="1" t="n">
         <v>2.78459602</v>
       </c>
-      <c r="I11" s="1" t="n">
+      <c r="I13" s="1" t="n">
         <v>14.78459602</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J13" s="1" t="n">
         <v>0.6421452136</v>
       </c>
-      <c r="K11" s="1" t="b">
+      <c r="K13" s="1" t="b">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:K11"/>
+  <autoFilter ref="A2:K13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>